--- a/research/traditional_assets/database/data/pakistan/pakistan_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_furn_home_furnishings.xlsx
@@ -1379,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1516,22 +1516,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1985940687006484</v>
+        <v>0.1980500959014166</v>
       </c>
       <c r="C2">
-        <v>35.67344188826912</v>
+        <v>35.46312380332331</v>
       </c>
       <c r="D2">
-        <v>35.42844188826912</v>
+        <v>35.55502380332331</v>
       </c>
       <c r="E2">
-        <v>-24.5</v>
+        <v>-24.1631</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3369</v>
       </c>
       <c r="G2">
         <v>0.245</v>
@@ -1552,28 +1552,28 @@
         <v>2.8425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01694607</v>
       </c>
       <c r="N2">
-        <v>2.8425</v>
+        <v>2.82555393</v>
       </c>
       <c r="O2">
-        <v>0.8243249999999999</v>
+        <v>0.8194106396999999</v>
       </c>
       <c r="P2">
-        <v>2.018175</v>
+        <v>2.0061432903</v>
       </c>
       <c r="Q2">
-        <v>3.088175</v>
+        <v>3.0761432903</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1985940687006484</v>
+        <v>0.1996898645468854</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9411712546318394</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>167.7380065112442</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1598,22 +1598,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1980500959014166</v>
+        <v>0.1975061231021847</v>
       </c>
       <c r="C3">
-        <v>35.46312380332331</v>
+        <v>35.25371348817949</v>
       </c>
       <c r="D3">
-        <v>35.55502380332331</v>
+        <v>35.6825134881795</v>
       </c>
       <c r="E3">
-        <v>-24.1631</v>
+        <v>-23.8262</v>
       </c>
       <c r="F3">
-        <v>0.3369</v>
+        <v>0.6738</v>
       </c>
       <c r="G3">
         <v>0.245</v>
@@ -1634,28 +1634,28 @@
         <v>2.8425</v>
       </c>
       <c r="M3">
-        <v>0.01694607</v>
+        <v>0.03389213999999999</v>
       </c>
       <c r="N3">
-        <v>2.82555393</v>
+        <v>2.80860786</v>
       </c>
       <c r="O3">
-        <v>0.8194106396999999</v>
+        <v>0.8144962793999999</v>
       </c>
       <c r="P3">
-        <v>2.0061432903</v>
+        <v>1.9941115806</v>
       </c>
       <c r="Q3">
-        <v>3.0761432903</v>
+        <v>3.0641115806</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1996898645468854</v>
+        <v>0.2008080235736578</v>
       </c>
       <c r="T3">
-        <v>0.9411712546318394</v>
+        <v>0.9480097760458647</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>167.7380065112442</v>
+        <v>83.86900325562212</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1680,22 +1680,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1975061231021847</v>
+        <v>0.1969621503029528</v>
       </c>
       <c r="C4">
-        <v>35.25371348817949</v>
+        <v>35.04522074295122</v>
       </c>
       <c r="D4">
-        <v>35.6825134881795</v>
+        <v>35.81092074295122</v>
       </c>
       <c r="E4">
-        <v>-23.8262</v>
+        <v>-23.4893</v>
       </c>
       <c r="F4">
-        <v>0.6738</v>
+        <v>1.0107</v>
       </c>
       <c r="G4">
         <v>0.245</v>
@@ -1716,28 +1716,28 @@
         <v>2.8425</v>
       </c>
       <c r="M4">
-        <v>0.03389213999999999</v>
+        <v>0.05083820999999999</v>
       </c>
       <c r="N4">
-        <v>2.80860786</v>
+        <v>2.79166179</v>
       </c>
       <c r="O4">
-        <v>0.8144962793999999</v>
+        <v>0.8095819191</v>
       </c>
       <c r="P4">
-        <v>1.9941115806</v>
+        <v>1.9820798709</v>
       </c>
       <c r="Q4">
-        <v>3.0641115806</v>
+        <v>3.0520798709</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2008080235736578</v>
+        <v>0.2019492374257245</v>
       </c>
       <c r="T4">
-        <v>0.9480097760458647</v>
+        <v>0.9549892979014163</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.86900325562212</v>
+        <v>55.91266883708141</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1762,22 +1762,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1969621503029528</v>
+        <v>0.1964181775037209</v>
       </c>
       <c r="C5">
-        <v>35.04522074295122</v>
+        <v>34.83765550932851</v>
       </c>
       <c r="D5">
-        <v>35.81092074295122</v>
+        <v>35.94025550932851</v>
       </c>
       <c r="E5">
-        <v>-23.4893</v>
+        <v>-23.1524</v>
       </c>
       <c r="F5">
-        <v>1.0107</v>
+        <v>1.3476</v>
       </c>
       <c r="G5">
         <v>0.245</v>
@@ -1798,28 +1798,28 @@
         <v>2.8425</v>
       </c>
       <c r="M5">
-        <v>0.05083820999999999</v>
+        <v>0.06778427999999999</v>
       </c>
       <c r="N5">
-        <v>2.79166179</v>
+        <v>2.77471572</v>
       </c>
       <c r="O5">
-        <v>0.8095819191</v>
+        <v>0.8046675587999998</v>
       </c>
       <c r="P5">
-        <v>1.9820798709</v>
+        <v>1.9700481612</v>
       </c>
       <c r="Q5">
-        <v>3.0520798709</v>
+        <v>3.0400481612</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2019492374257245</v>
+        <v>0.2031142265663759</v>
       </c>
       <c r="T5">
-        <v>0.9549892979014163</v>
+        <v>0.9621142264622916</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.91266883708141</v>
+        <v>41.93450162781105</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1844,22 +1844,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1964181775037209</v>
+        <v>0.195874204704489</v>
       </c>
       <c r="C6">
-        <v>34.83765550932851</v>
+        <v>34.63102787314355</v>
       </c>
       <c r="D6">
-        <v>35.94025550932851</v>
+        <v>36.07052787314355</v>
       </c>
       <c r="E6">
-        <v>-23.1524</v>
+        <v>-22.8155</v>
       </c>
       <c r="F6">
-        <v>1.3476</v>
+        <v>1.6845</v>
       </c>
       <c r="G6">
         <v>0.245</v>
@@ -1880,28 +1880,28 @@
         <v>2.8425</v>
       </c>
       <c r="M6">
-        <v>0.06778427999999999</v>
+        <v>0.08473035</v>
       </c>
       <c r="N6">
-        <v>2.77471572</v>
+        <v>2.75776965</v>
       </c>
       <c r="O6">
-        <v>0.8046675587999998</v>
+        <v>0.7997531984999998</v>
       </c>
       <c r="P6">
-        <v>1.9700481612</v>
+        <v>1.9580164515</v>
       </c>
       <c r="Q6">
-        <v>3.0400481612</v>
+        <v>3.0280164515</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2031142265663759</v>
+        <v>0.204303741794199</v>
       </c>
       <c r="T6">
-        <v>0.9621142264622916</v>
+        <v>0.9693891535191855</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.93450162781105</v>
+        <v>33.54760130224884</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1926,22 +1926,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.195874204704489</v>
+        <v>0.1953302319052571</v>
       </c>
       <c r="C7">
-        <v>34.63102787314355</v>
+        <v>34.42534806699276</v>
       </c>
       <c r="D7">
-        <v>36.07052787314355</v>
+        <v>36.20174806699276</v>
       </c>
       <c r="E7">
-        <v>-22.8155</v>
+        <v>-22.4786</v>
       </c>
       <c r="F7">
-        <v>1.6845</v>
+        <v>2.0214</v>
       </c>
       <c r="G7">
         <v>0.245</v>
@@ -1962,28 +1962,28 @@
         <v>2.8425</v>
       </c>
       <c r="M7">
-        <v>0.08473035</v>
+        <v>0.10167642</v>
       </c>
       <c r="N7">
-        <v>2.75776965</v>
+        <v>2.74082358</v>
       </c>
       <c r="O7">
-        <v>0.7997531984999998</v>
+        <v>0.7948388381999999</v>
       </c>
       <c r="P7">
-        <v>1.9580164515</v>
+        <v>1.9459847418</v>
       </c>
       <c r="Q7">
-        <v>3.0280164515</v>
+        <v>3.0159847418</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.204303741794199</v>
+        <v>0.2055185658566565</v>
       </c>
       <c r="T7">
-        <v>0.9693891535191855</v>
+        <v>0.9768188662581411</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.54760130224884</v>
+        <v>27.9563344185407</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2008,22 +2008,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1953302319052571</v>
+        <v>0.1947862591060253</v>
       </c>
       <c r="C8">
-        <v>34.42534806699276</v>
+        <v>34.22062647291591</v>
       </c>
       <c r="D8">
-        <v>36.20174806699276</v>
+        <v>36.33392647291591</v>
       </c>
       <c r="E8">
-        <v>-22.4786</v>
+        <v>-22.1417</v>
       </c>
       <c r="F8">
-        <v>2.0214</v>
+        <v>2.358299999999999</v>
       </c>
       <c r="G8">
         <v>0.245</v>
@@ -2044,28 +2044,28 @@
         <v>2.8425</v>
       </c>
       <c r="M8">
-        <v>0.10167642</v>
+        <v>0.11862249</v>
       </c>
       <c r="N8">
-        <v>2.74082358</v>
+        <v>2.72387751</v>
       </c>
       <c r="O8">
-        <v>0.7948388381999999</v>
+        <v>0.7899244778999999</v>
       </c>
       <c r="P8">
-        <v>1.9459847418</v>
+        <v>1.9339530321</v>
       </c>
       <c r="Q8">
-        <v>3.0159847418</v>
+        <v>3.0039530321</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2055185658566565</v>
+        <v>0.2067595151677691</v>
       </c>
       <c r="T8">
-        <v>0.9768188662581411</v>
+        <v>0.9844083577656764</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.9563344185407</v>
+        <v>23.96257235874918</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2090,22 +2090,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1947862591060253</v>
+        <v>0.1942422863067934</v>
       </c>
       <c r="C9">
-        <v>34.22062647291592</v>
+        <v>34.01687362513445</v>
       </c>
       <c r="D9">
-        <v>36.33392647291592</v>
+        <v>36.46707362513445</v>
       </c>
       <c r="E9">
-        <v>-22.1417</v>
+        <v>-21.8048</v>
       </c>
       <c r="F9">
-        <v>2.3583</v>
+        <v>2.6952</v>
       </c>
       <c r="G9">
         <v>0.245</v>
@@ -2126,28 +2126,28 @@
         <v>2.8425</v>
       </c>
       <c r="M9">
-        <v>0.11862249</v>
+        <v>0.13556856</v>
       </c>
       <c r="N9">
-        <v>2.72387751</v>
+        <v>2.70693144</v>
       </c>
       <c r="O9">
-        <v>0.7899244778999999</v>
+        <v>0.7850101175999999</v>
       </c>
       <c r="P9">
-        <v>1.9339530321</v>
+        <v>1.9219213224</v>
       </c>
       <c r="Q9">
-        <v>3.0039530321</v>
+        <v>2.9919213224</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2067595151677691</v>
+        <v>0.2080274416378189</v>
       </c>
       <c r="T9">
-        <v>0.9844083577656764</v>
+        <v>0.9921628382190274</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.96257235874917</v>
+        <v>20.96725081390553</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2172,22 +2172,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1942422863067934</v>
+        <v>0.1936983135075615</v>
       </c>
       <c r="C10">
-        <v>34.01687362513445</v>
+        <v>33.81410021285004</v>
       </c>
       <c r="D10">
-        <v>36.46707362513445</v>
+        <v>36.60120021285005</v>
       </c>
       <c r="E10">
-        <v>-21.8048</v>
+        <v>-21.4679</v>
       </c>
       <c r="F10">
-        <v>2.6952</v>
+        <v>3.0321</v>
       </c>
       <c r="G10">
         <v>0.245</v>
@@ -2208,28 +2208,28 @@
         <v>2.8425</v>
       </c>
       <c r="M10">
-        <v>0.13556856</v>
+        <v>0.15251463</v>
       </c>
       <c r="N10">
-        <v>2.70693144</v>
+        <v>2.68998537</v>
       </c>
       <c r="O10">
-        <v>0.7850101175999999</v>
+        <v>0.7800957572999998</v>
       </c>
       <c r="P10">
-        <v>1.9219213224</v>
+        <v>1.9098896127</v>
       </c>
       <c r="Q10">
-        <v>2.9919213224</v>
+        <v>2.9798896127</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2080274416378189</v>
+        <v>0.2093232346236939</v>
       </c>
       <c r="T10">
-        <v>0.9921628382190274</v>
+        <v>1.00008774681421</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.96725081390553</v>
+        <v>18.63755627902713</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2254,22 +2254,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1936983135075615</v>
+        <v>0.1931543407083296</v>
       </c>
       <c r="C11">
-        <v>33.81410021285004</v>
+        <v>33.61231708310525</v>
       </c>
       <c r="D11">
-        <v>36.60120021285005</v>
+        <v>36.73631708310526</v>
       </c>
       <c r="E11">
-        <v>-21.4679</v>
+        <v>-21.131</v>
       </c>
       <c r="F11">
-        <v>3.0321</v>
+        <v>3.368999999999999</v>
       </c>
       <c r="G11">
         <v>0.245</v>
@@ -2290,28 +2290,28 @@
         <v>2.8425</v>
       </c>
       <c r="M11">
-        <v>0.15251463</v>
+        <v>0.1694607</v>
       </c>
       <c r="N11">
-        <v>2.68998537</v>
+        <v>2.6730393</v>
       </c>
       <c r="O11">
-        <v>0.7800957572999998</v>
+        <v>0.7751813969999999</v>
       </c>
       <c r="P11">
-        <v>1.9098896127</v>
+        <v>1.897857903</v>
       </c>
       <c r="Q11">
-        <v>2.9798896127</v>
+        <v>2.967857903</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2093232346236939</v>
+        <v>0.2106478230092551</v>
       </c>
       <c r="T11">
-        <v>1.00008774681421</v>
+        <v>1.008188764489287</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.63755627902713</v>
+        <v>16.77380065112442</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2336,22 +2336,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1931543407083296</v>
+        <v>0.1926103679090978</v>
       </c>
       <c r="C12">
-        <v>33.61231708310525</v>
+        <v>33.41153524370778</v>
       </c>
       <c r="D12">
-        <v>36.73631708310526</v>
+        <v>36.87243524370778</v>
       </c>
       <c r="E12">
-        <v>-21.131</v>
+        <v>-20.7941</v>
       </c>
       <c r="F12">
-        <v>3.369</v>
+        <v>3.7059</v>
       </c>
       <c r="G12">
         <v>0.245</v>
@@ -2372,28 +2372,28 @@
         <v>2.8425</v>
       </c>
       <c r="M12">
-        <v>0.1694607</v>
+        <v>0.18640677</v>
       </c>
       <c r="N12">
-        <v>2.6730393</v>
+        <v>2.65609323</v>
       </c>
       <c r="O12">
-        <v>0.7751813969999999</v>
+        <v>0.7702670366999999</v>
       </c>
       <c r="P12">
-        <v>1.897857903</v>
+        <v>1.8858261933</v>
       </c>
       <c r="Q12">
-        <v>2.967857903</v>
+        <v>2.9558261933</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2106478230092551</v>
+        <v>0.2120021774259525</v>
       </c>
       <c r="T12">
-        <v>1.008188764489287</v>
+        <v>1.016471827505376</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.77380065112442</v>
+        <v>15.24890968284038</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2418,22 +2418,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1926103679090978</v>
+        <v>0.1920663951098658</v>
       </c>
       <c r="C13">
-        <v>33.41153524370778</v>
+        <v>33.21176586621988</v>
       </c>
       <c r="D13">
-        <v>36.87243524370778</v>
+        <v>37.00956586621989</v>
       </c>
       <c r="E13">
-        <v>-20.7941</v>
+        <v>-20.4572</v>
       </c>
       <c r="F13">
-        <v>3.7059</v>
+        <v>4.0428</v>
       </c>
       <c r="G13">
         <v>0.245</v>
@@ -2454,28 +2454,28 @@
         <v>2.8425</v>
       </c>
       <c r="M13">
-        <v>0.18640677</v>
+        <v>0.20335284</v>
       </c>
       <c r="N13">
-        <v>2.65609323</v>
+        <v>2.63914716</v>
       </c>
       <c r="O13">
-        <v>0.7702670366999999</v>
+        <v>0.7653526763999999</v>
       </c>
       <c r="P13">
-        <v>1.8858261933</v>
+        <v>1.8737944836</v>
       </c>
       <c r="Q13">
-        <v>2.9558261933</v>
+        <v>2.9437944836</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2120021774259525</v>
+        <v>0.2133873126248476</v>
       </c>
       <c r="T13">
-        <v>1.016471827505376</v>
+        <v>1.024943141953648</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.24890968284038</v>
+        <v>13.97816720927035</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2500,22 +2500,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1920663951098658</v>
+        <v>0.191522422310634</v>
       </c>
       <c r="C14">
-        <v>33.21176586621988</v>
+        <v>33.0130202890148</v>
       </c>
       <c r="D14">
-        <v>37.00956586621989</v>
+        <v>37.14772028901481</v>
       </c>
       <c r="E14">
-        <v>-20.4572</v>
+        <v>-20.1203</v>
       </c>
       <c r="F14">
-        <v>4.0428</v>
+        <v>4.3797</v>
       </c>
       <c r="G14">
         <v>0.245</v>
@@ -2536,28 +2536,28 @@
         <v>2.8425</v>
       </c>
       <c r="M14">
-        <v>0.20335284</v>
+        <v>0.22029891</v>
       </c>
       <c r="N14">
-        <v>2.63914716</v>
+        <v>2.62220109</v>
       </c>
       <c r="O14">
-        <v>0.7653526763999999</v>
+        <v>0.7604383160999999</v>
       </c>
       <c r="P14">
-        <v>1.8737944836</v>
+        <v>1.8617627739</v>
       </c>
       <c r="Q14">
-        <v>2.9437944836</v>
+        <v>2.9317627739</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2133873126248476</v>
+        <v>0.214804290012223</v>
       </c>
       <c r="T14">
-        <v>1.024943141953648</v>
+        <v>1.033609199262801</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.97816720927035</v>
+        <v>12.90292357778802</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2582,22 +2582,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.191522422310634</v>
+        <v>0.1911275495114021</v>
       </c>
       <c r="C15">
-        <v>33.0130202890148</v>
+        <v>32.77705520703224</v>
       </c>
       <c r="D15">
-        <v>37.14772028901481</v>
+        <v>37.24865520703224</v>
       </c>
       <c r="E15">
-        <v>-20.1203</v>
+        <v>-19.7834</v>
       </c>
       <c r="F15">
-        <v>4.3797</v>
+        <v>4.716600000000001</v>
       </c>
       <c r="G15">
         <v>0.245</v>
@@ -2618,45 +2618,45 @@
         <v>2.8425</v>
       </c>
       <c r="M15">
-        <v>0.22029891</v>
+        <v>0.24431988</v>
       </c>
       <c r="N15">
-        <v>2.62220109</v>
+        <v>2.59818012</v>
       </c>
       <c r="O15">
-        <v>0.7604383160999999</v>
+        <v>0.7534722347999999</v>
       </c>
       <c r="P15">
-        <v>1.8617627739</v>
+        <v>1.8447078852</v>
       </c>
       <c r="Q15">
-        <v>2.9317627739</v>
+        <v>2.9147078852</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.214804290012223</v>
+        <v>0.2162542203620954</v>
       </c>
       <c r="T15">
-        <v>1.033609199262801</v>
+        <v>1.042476792788446</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.29</v>
       </c>
       <c r="W15">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.90292357778802</v>
+        <v>11.6343377378869</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2664,22 +2664,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1911275495114021</v>
+        <v>0.1905942267121702</v>
       </c>
       <c r="C16">
-        <v>32.77705520703224</v>
+        <v>32.57735375088113</v>
       </c>
       <c r="D16">
-        <v>37.24865520703224</v>
+        <v>37.38585375088113</v>
       </c>
       <c r="E16">
-        <v>-19.7834</v>
+        <v>-19.4465</v>
       </c>
       <c r="F16">
-        <v>4.716600000000001</v>
+        <v>5.053500000000001</v>
       </c>
       <c r="G16">
         <v>0.245</v>
@@ -2700,28 +2700,28 @@
         <v>2.8425</v>
       </c>
       <c r="M16">
-        <v>0.24431988</v>
+        <v>0.2617713</v>
       </c>
       <c r="N16">
-        <v>2.59818012</v>
+        <v>2.5807287</v>
       </c>
       <c r="O16">
-        <v>0.7534722347999999</v>
+        <v>0.7484113229999999</v>
       </c>
       <c r="P16">
-        <v>1.8447078852</v>
+        <v>1.832317377</v>
       </c>
       <c r="Q16">
-        <v>2.9147078852</v>
+        <v>2.902317377</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2162542203620954</v>
+        <v>0.2177382667202003</v>
       </c>
       <c r="T16">
-        <v>1.042476792788446</v>
+        <v>1.051553035573517</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.6343377378869</v>
+        <v>10.85871522202778</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2746,22 +2746,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1905942267121702</v>
+        <v>0.1900609039129383</v>
       </c>
       <c r="C17">
-        <v>32.57735375088113</v>
+        <v>32.37866672219405</v>
       </c>
       <c r="D17">
-        <v>37.38585375088113</v>
+        <v>37.52406672219406</v>
       </c>
       <c r="E17">
-        <v>-19.4465</v>
+        <v>-19.1096</v>
       </c>
       <c r="F17">
-        <v>5.0535</v>
+        <v>5.3904</v>
       </c>
       <c r="G17">
         <v>0.245</v>
@@ -2782,28 +2782,28 @@
         <v>2.8425</v>
       </c>
       <c r="M17">
-        <v>0.2617713</v>
+        <v>0.27922272</v>
       </c>
       <c r="N17">
-        <v>2.5807287</v>
+        <v>2.56327728</v>
       </c>
       <c r="O17">
-        <v>0.7484113229999999</v>
+        <v>0.7433504111999999</v>
       </c>
       <c r="P17">
-        <v>1.832317377</v>
+        <v>1.8199268688</v>
       </c>
       <c r="Q17">
-        <v>2.902317377</v>
+        <v>2.8899268688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2177382667202003</v>
+        <v>0.2192576475154028</v>
       </c>
       <c r="T17">
-        <v>1.051553035573517</v>
+        <v>1.060845379377281</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.85871522202778</v>
+        <v>10.18004552065104</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2828,22 +2828,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1900609039129383</v>
+        <v>0.1897327711137065</v>
       </c>
       <c r="C18">
-        <v>32.37866672219405</v>
+        <v>32.12731275147456</v>
       </c>
       <c r="D18">
-        <v>37.52406672219406</v>
+        <v>37.60961275147456</v>
       </c>
       <c r="E18">
-        <v>-19.1096</v>
+        <v>-18.7727</v>
       </c>
       <c r="F18">
-        <v>5.3904</v>
+        <v>5.7273</v>
       </c>
       <c r="G18">
         <v>0.245</v>
@@ -2864,45 +2864,45 @@
         <v>2.8425</v>
       </c>
       <c r="M18">
-        <v>0.27922272</v>
+        <v>0.3064105499999999</v>
       </c>
       <c r="N18">
-        <v>2.56327728</v>
+        <v>2.53608945</v>
       </c>
       <c r="O18">
-        <v>0.7433504111999999</v>
+        <v>0.7354659404999999</v>
       </c>
       <c r="P18">
-        <v>1.8199268688</v>
+        <v>1.8006235095</v>
       </c>
       <c r="Q18">
-        <v>2.8899268688</v>
+        <v>2.8706235095</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2192576475154028</v>
+        <v>0.2208136398960319</v>
       </c>
       <c r="T18">
-        <v>1.060845379377281</v>
+        <v>1.07036163507993</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.29</v>
       </c>
       <c r="W18">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.18004552065104</v>
+        <v>9.276769354057818</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2910,22 +2910,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1897327711137065</v>
+        <v>0.1892115183144746</v>
       </c>
       <c r="C19">
-        <v>32.12731275147456</v>
+        <v>31.92711108752972</v>
       </c>
       <c r="D19">
-        <v>37.60961275147456</v>
+        <v>37.74631108752972</v>
       </c>
       <c r="E19">
-        <v>-18.7727</v>
+        <v>-18.4358</v>
       </c>
       <c r="F19">
-        <v>5.7273</v>
+        <v>6.0642</v>
       </c>
       <c r="G19">
         <v>0.245</v>
@@ -2946,28 +2946,28 @@
         <v>2.8425</v>
       </c>
       <c r="M19">
-        <v>0.3064105499999999</v>
+        <v>0.3244347</v>
       </c>
       <c r="N19">
-        <v>2.53608945</v>
+        <v>2.5180653</v>
       </c>
       <c r="O19">
-        <v>0.7354659404999999</v>
+        <v>0.730238937</v>
       </c>
       <c r="P19">
-        <v>1.8006235095</v>
+        <v>1.787826363</v>
       </c>
       <c r="Q19">
-        <v>2.8706235095</v>
+        <v>2.857826363</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2208136398960319</v>
+        <v>0.2224075833103349</v>
       </c>
       <c r="T19">
-        <v>1.07036163507993</v>
+        <v>1.080109994580206</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.276769354057818</v>
+        <v>8.761393278832381</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2992,22 +2992,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1892115183144746</v>
+        <v>0.1886902655152427</v>
       </c>
       <c r="C20">
-        <v>31.92711108752971</v>
+        <v>31.72790675380974</v>
       </c>
       <c r="D20">
-        <v>37.74631108752971</v>
+        <v>37.88400675380974</v>
       </c>
       <c r="E20">
-        <v>-18.4358</v>
+        <v>-18.0989</v>
       </c>
       <c r="F20">
-        <v>6.0642</v>
+        <v>6.4011</v>
       </c>
       <c r="G20">
         <v>0.245</v>
@@ -3028,28 +3028,28 @@
         <v>2.8425</v>
       </c>
       <c r="M20">
-        <v>0.3244347</v>
+        <v>0.34245885</v>
       </c>
       <c r="N20">
-        <v>2.5180653</v>
+        <v>2.50004115</v>
       </c>
       <c r="O20">
-        <v>0.730238937</v>
+        <v>0.7250119334999999</v>
       </c>
       <c r="P20">
-        <v>1.787826363</v>
+        <v>1.7750292165</v>
       </c>
       <c r="Q20">
-        <v>2.857826363</v>
+        <v>2.8450292165</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2224075833103349</v>
+        <v>0.2240408833521515</v>
       </c>
       <c r="T20">
-        <v>1.080109994580206</v>
+        <v>1.090099054315055</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.761393278832383</v>
+        <v>8.300267316788572</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3074,22 +3074,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1886902655152427</v>
+        <v>0.1881690127160108</v>
       </c>
       <c r="C21">
-        <v>31.72790675380974</v>
+        <v>31.52971070482985</v>
       </c>
       <c r="D21">
-        <v>37.88400675380974</v>
+        <v>38.02271070482985</v>
       </c>
       <c r="E21">
-        <v>-18.0989</v>
+        <v>-17.762</v>
       </c>
       <c r="F21">
-        <v>6.4011</v>
+        <v>6.738</v>
       </c>
       <c r="G21">
         <v>0.245</v>
@@ -3110,28 +3110,28 @@
         <v>2.8425</v>
       </c>
       <c r="M21">
-        <v>0.34245885</v>
+        <v>0.3604829999999999</v>
       </c>
       <c r="N21">
-        <v>2.50004115</v>
+        <v>2.482017</v>
       </c>
       <c r="O21">
-        <v>0.7250119334999999</v>
+        <v>0.7197849299999999</v>
       </c>
       <c r="P21">
-        <v>1.7750292165</v>
+        <v>1.76223207</v>
       </c>
       <c r="Q21">
-        <v>2.8450292165</v>
+        <v>2.83223207</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2240408833521515</v>
+        <v>0.2257150158950135</v>
       </c>
       <c r="T21">
-        <v>1.090099054315055</v>
+        <v>1.100337840543276</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.300267316788572</v>
+        <v>7.885253950949144</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3156,22 +3156,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1881690127160108</v>
+        <v>0.187767039916779</v>
       </c>
       <c r="C22">
-        <v>31.52971070482985</v>
+        <v>31.30047016906439</v>
       </c>
       <c r="D22">
-        <v>38.02271070482985</v>
+        <v>38.13037016906439</v>
       </c>
       <c r="E22">
-        <v>-17.762</v>
+        <v>-17.4251</v>
       </c>
       <c r="F22">
-        <v>6.738</v>
+        <v>7.0749</v>
       </c>
       <c r="G22">
         <v>0.245</v>
@@ -3192,45 +3192,45 @@
         <v>2.8425</v>
       </c>
       <c r="M22">
-        <v>0.3604829999999999</v>
+        <v>0.3841670700000001</v>
       </c>
       <c r="N22">
-        <v>2.482017</v>
+        <v>2.45833293</v>
       </c>
       <c r="O22">
-        <v>0.7197849299999999</v>
+        <v>0.7129165496999998</v>
       </c>
       <c r="P22">
-        <v>1.76223207</v>
+        <v>1.7454163803</v>
       </c>
       <c r="Q22">
-        <v>2.83223207</v>
+        <v>2.815416380299999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2257150158950135</v>
+        <v>0.2274315315402265</v>
       </c>
       <c r="T22">
-        <v>1.100337840543276</v>
+        <v>1.110835836549427</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.29</v>
       </c>
       <c r="W22">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.885253950949144</v>
+        <v>7.399124552762941</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3238,22 +3238,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.187767039916779</v>
+        <v>0.1872514671175471</v>
       </c>
       <c r="C23">
-        <v>31.30047016906439</v>
+        <v>31.10255057050113</v>
       </c>
       <c r="D23">
-        <v>38.13037016906439</v>
+        <v>38.26935057050113</v>
       </c>
       <c r="E23">
-        <v>-17.4251</v>
+        <v>-17.0882</v>
       </c>
       <c r="F23">
-        <v>7.0749</v>
+        <v>7.411799999999999</v>
       </c>
       <c r="G23">
         <v>0.245</v>
@@ -3274,28 +3274,28 @@
         <v>2.8425</v>
       </c>
       <c r="M23">
-        <v>0.38416707</v>
+        <v>0.40246074</v>
       </c>
       <c r="N23">
-        <v>2.45833293</v>
+        <v>2.44003926</v>
       </c>
       <c r="O23">
-        <v>0.7129165496999998</v>
+        <v>0.7076113853999999</v>
       </c>
       <c r="P23">
-        <v>1.7454163803</v>
+        <v>1.7324278746</v>
       </c>
       <c r="Q23">
-        <v>2.815416380299999</v>
+        <v>2.8024278746</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2274315315402265</v>
+        <v>0.2291920604071116</v>
       </c>
       <c r="T23">
-        <v>1.110835836549427</v>
+        <v>1.121603011940351</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.399124552762942</v>
+        <v>7.062800709455535</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3320,22 +3320,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1872514671175471</v>
+        <v>0.1867358943183152</v>
       </c>
       <c r="C24">
-        <v>31.10255057050113</v>
+        <v>30.90564781033739</v>
       </c>
       <c r="D24">
-        <v>38.26935057050113</v>
+        <v>38.40934781033739</v>
       </c>
       <c r="E24">
-        <v>-17.0882</v>
+        <v>-16.7513</v>
       </c>
       <c r="F24">
-        <v>7.411799999999999</v>
+        <v>7.748699999999999</v>
       </c>
       <c r="G24">
         <v>0.245</v>
@@ -3356,28 +3356,28 @@
         <v>2.8425</v>
       </c>
       <c r="M24">
-        <v>0.40246074</v>
+        <v>0.42075441</v>
       </c>
       <c r="N24">
-        <v>2.44003926</v>
+        <v>2.42174559</v>
       </c>
       <c r="O24">
-        <v>0.7076113853999999</v>
+        <v>0.7023062211</v>
       </c>
       <c r="P24">
-        <v>1.7324278746</v>
+        <v>1.7194393689</v>
       </c>
       <c r="Q24">
-        <v>2.8024278746</v>
+        <v>2.7894393689</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2291920604071116</v>
+        <v>0.2309983172965132</v>
       </c>
       <c r="T24">
-        <v>1.121603011940351</v>
+        <v>1.132649854224546</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.062800709455535</v>
+        <v>6.755722417740079</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3402,22 +3402,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1867358943183152</v>
+        <v>0.1862203215190833</v>
       </c>
       <c r="C25">
-        <v>30.90564781033739</v>
+        <v>30.70977308896529</v>
       </c>
       <c r="D25">
-        <v>38.40934781033739</v>
+        <v>38.55037308896529</v>
       </c>
       <c r="E25">
-        <v>-16.7513</v>
+        <v>-16.4144</v>
       </c>
       <c r="F25">
-        <v>7.748699999999999</v>
+        <v>8.085599999999999</v>
       </c>
       <c r="G25">
         <v>0.245</v>
@@ -3438,28 +3438,28 @@
         <v>2.8425</v>
       </c>
       <c r="M25">
-        <v>0.42075441</v>
+        <v>0.43904808</v>
       </c>
       <c r="N25">
-        <v>2.42174559</v>
+        <v>2.40345192</v>
       </c>
       <c r="O25">
-        <v>0.7023062211</v>
+        <v>0.6970010567999999</v>
       </c>
       <c r="P25">
-        <v>1.7194393689</v>
+        <v>1.7064508632</v>
       </c>
       <c r="Q25">
-        <v>2.7894393689</v>
+        <v>2.7764508632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2309983172965132</v>
+        <v>0.2328521072619517</v>
       </c>
       <c r="T25">
-        <v>1.132649854224546</v>
+        <v>1.14398740288464</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.755722417740079</v>
+        <v>6.474233983667575</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3484,22 +3484,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1862203215190833</v>
+        <v>0.1857047487198514</v>
       </c>
       <c r="C26">
-        <v>30.70977308896529</v>
+        <v>30.51493777187831</v>
       </c>
       <c r="D26">
-        <v>38.55037308896529</v>
+        <v>38.69243777187831</v>
       </c>
       <c r="E26">
-        <v>-16.4144</v>
+        <v>-16.0775</v>
       </c>
       <c r="F26">
-        <v>8.085599999999999</v>
+        <v>8.422499999999999</v>
       </c>
       <c r="G26">
         <v>0.245</v>
@@ -3520,28 +3520,28 @@
         <v>2.8425</v>
       </c>
       <c r="M26">
-        <v>0.43904808</v>
+        <v>0.45734175</v>
       </c>
       <c r="N26">
-        <v>2.40345192</v>
+        <v>2.38515825</v>
       </c>
       <c r="O26">
-        <v>0.6970010567999999</v>
+        <v>0.6916958925</v>
       </c>
       <c r="P26">
-        <v>1.7064508632</v>
+        <v>1.6934623575</v>
       </c>
       <c r="Q26">
-        <v>2.7764508632</v>
+        <v>2.7634623575</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2328521072619517</v>
+        <v>0.2347553316264686</v>
       </c>
       <c r="T26">
-        <v>1.14398740288464</v>
+        <v>1.15562728617567</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.474233983667575</v>
+        <v>6.215264624320872</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3566,22 +3566,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1857047487198514</v>
+        <v>0.1853737759206195</v>
       </c>
       <c r="C27">
-        <v>30.51493777187831</v>
+        <v>30.26978956661191</v>
       </c>
       <c r="D27">
-        <v>38.69243777187831</v>
+        <v>38.78418956661191</v>
       </c>
       <c r="E27">
-        <v>-16.0775</v>
+        <v>-15.7406</v>
       </c>
       <c r="F27">
-        <v>8.422499999999999</v>
+        <v>8.759399999999999</v>
       </c>
       <c r="G27">
         <v>0.245</v>
@@ -3602,45 +3602,45 @@
         <v>2.8425</v>
       </c>
       <c r="M27">
-        <v>0.45734175</v>
+        <v>0.48439482</v>
       </c>
       <c r="N27">
-        <v>2.38515825</v>
+        <v>2.35810518</v>
       </c>
       <c r="O27">
-        <v>0.6916958925</v>
+        <v>0.6838505021999999</v>
       </c>
       <c r="P27">
-        <v>1.6934623575</v>
+        <v>1.6742546778</v>
       </c>
       <c r="Q27">
-        <v>2.7634623575</v>
+        <v>2.7442546778</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2347553316264686</v>
+        <v>0.2367099944873237</v>
       </c>
       <c r="T27">
-        <v>1.15562728617567</v>
+        <v>1.167581760906999</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.29</v>
       </c>
       <c r="W27">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.215264624320872</v>
+        <v>5.868146979771583</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3648,22 +3648,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1853737759206195</v>
+        <v>0.1848653031213877</v>
       </c>
       <c r="C28">
-        <v>30.26978956661191</v>
+        <v>30.0746985224926</v>
       </c>
       <c r="D28">
-        <v>38.78418956661191</v>
+        <v>38.92599852249261</v>
       </c>
       <c r="E28">
-        <v>-15.7406</v>
+        <v>-15.4037</v>
       </c>
       <c r="F28">
-        <v>8.759399999999999</v>
+        <v>9.096299999999999</v>
       </c>
       <c r="G28">
         <v>0.245</v>
@@ -3684,28 +3684,28 @@
         <v>2.8425</v>
       </c>
       <c r="M28">
-        <v>0.48439482</v>
+        <v>0.50302539</v>
       </c>
       <c r="N28">
-        <v>2.35810518</v>
+        <v>2.33947461</v>
       </c>
       <c r="O28">
-        <v>0.6838505021999999</v>
+        <v>0.6784476368999999</v>
       </c>
       <c r="P28">
-        <v>1.6742546778</v>
+        <v>1.6610269731</v>
       </c>
       <c r="Q28">
-        <v>2.7442546778</v>
+        <v>2.7310269731</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2367099944873237</v>
+        <v>0.2387182097553256</v>
       </c>
       <c r="T28">
-        <v>1.167581760906999</v>
+        <v>1.17986375549398</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.868146979771583</v>
+        <v>5.650808202743006</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3730,22 +3730,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1848653031213877</v>
+        <v>0.1843568303221558</v>
       </c>
       <c r="C29">
-        <v>30.0746985224926</v>
+        <v>29.88064829312902</v>
       </c>
       <c r="D29">
-        <v>38.92599852249261</v>
+        <v>39.06884829312902</v>
       </c>
       <c r="E29">
-        <v>-15.4037</v>
+        <v>-15.0668</v>
       </c>
       <c r="F29">
-        <v>9.096299999999999</v>
+        <v>9.433200000000001</v>
       </c>
       <c r="G29">
         <v>0.245</v>
@@ -3766,28 +3766,28 @@
         <v>2.8425</v>
       </c>
       <c r="M29">
-        <v>0.50302539</v>
+        <v>0.52165596</v>
       </c>
       <c r="N29">
-        <v>2.33947461</v>
+        <v>2.32084404</v>
       </c>
       <c r="O29">
-        <v>0.6784476368999999</v>
+        <v>0.6730447715999999</v>
       </c>
       <c r="P29">
-        <v>1.6610269731</v>
+        <v>1.6477992684</v>
       </c>
       <c r="Q29">
-        <v>2.7310269731</v>
+        <v>2.7177992684</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2387182097553256</v>
+        <v>0.2407822087807719</v>
       </c>
       <c r="T29">
-        <v>1.17986375549398</v>
+        <v>1.192486916597266</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.650808202743006</v>
+        <v>5.448993624073613</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3812,22 +3812,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1843568303221558</v>
+        <v>0.1838483575229239</v>
       </c>
       <c r="C30">
-        <v>29.88064829312902</v>
+        <v>29.68765037940391</v>
       </c>
       <c r="D30">
-        <v>39.06884829312902</v>
+        <v>39.21275037940391</v>
       </c>
       <c r="E30">
-        <v>-15.0668</v>
+        <v>-14.7299</v>
       </c>
       <c r="F30">
-        <v>9.433200000000001</v>
+        <v>9.770100000000001</v>
       </c>
       <c r="G30">
         <v>0.245</v>
@@ -3848,28 +3848,28 @@
         <v>2.8425</v>
       </c>
       <c r="M30">
-        <v>0.52165596</v>
+        <v>0.54028653</v>
       </c>
       <c r="N30">
-        <v>2.32084404</v>
+        <v>2.30221347</v>
       </c>
       <c r="O30">
-        <v>0.6730447715999999</v>
+        <v>0.6676419062999999</v>
       </c>
       <c r="P30">
-        <v>1.6477992684</v>
+        <v>1.6345715637</v>
       </c>
       <c r="Q30">
-        <v>2.7177992684</v>
+        <v>2.7045715637</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2407822087807719</v>
+        <v>0.2429043486238365</v>
       </c>
       <c r="T30">
-        <v>1.192486916597266</v>
+        <v>1.205465659703462</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.448993624073613</v>
+        <v>5.261097292209006</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3894,22 +3894,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1838483575229239</v>
+        <v>0.183339884723692</v>
       </c>
       <c r="C31">
-        <v>29.68765037940391</v>
+        <v>29.49571645227109</v>
       </c>
       <c r="D31">
-        <v>39.21275037940391</v>
+        <v>39.35771645227109</v>
       </c>
       <c r="E31">
-        <v>-14.7299</v>
+        <v>-14.393</v>
       </c>
       <c r="F31">
-        <v>9.770099999999999</v>
+        <v>10.107</v>
       </c>
       <c r="G31">
         <v>0.245</v>
@@ -3930,28 +3930,28 @@
         <v>2.8425</v>
       </c>
       <c r="M31">
-        <v>0.5402865299999999</v>
+        <v>0.5589170999999999</v>
       </c>
       <c r="N31">
-        <v>2.30221347</v>
+        <v>2.2835829</v>
       </c>
       <c r="O31">
-        <v>0.6676419062999999</v>
+        <v>0.6622390409999999</v>
       </c>
       <c r="P31">
-        <v>1.6345715637</v>
+        <v>1.621343859</v>
       </c>
       <c r="Q31">
-        <v>2.7045715637</v>
+        <v>2.691343859</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2429043486238365</v>
+        <v>0.2450871210338457</v>
       </c>
       <c r="T31">
-        <v>1.205465659703462</v>
+        <v>1.218815224041264</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.261097292209007</v>
+        <v>5.085727382468706</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3976,22 +3976,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.183339884723692</v>
+        <v>0.1828314119244601</v>
       </c>
       <c r="C32">
-        <v>29.49571645227109</v>
+        <v>29.30485835591062</v>
       </c>
       <c r="D32">
-        <v>39.35771645227109</v>
+        <v>39.50375835591063</v>
       </c>
       <c r="E32">
-        <v>-14.393</v>
+        <v>-14.0561</v>
       </c>
       <c r="F32">
-        <v>10.107</v>
+        <v>10.4439</v>
       </c>
       <c r="G32">
         <v>0.245</v>
@@ -4012,28 +4012,28 @@
         <v>2.8425</v>
       </c>
       <c r="M32">
-        <v>0.5589170999999999</v>
+        <v>0.57754767</v>
       </c>
       <c r="N32">
-        <v>2.2835829</v>
+        <v>2.26495233</v>
       </c>
       <c r="O32">
-        <v>0.6622390409999999</v>
+        <v>0.6568361756999999</v>
       </c>
       <c r="P32">
-        <v>1.621343859</v>
+        <v>1.6081161543</v>
       </c>
       <c r="Q32">
-        <v>2.691343859</v>
+        <v>2.6781161543</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2450871210338457</v>
+        <v>0.2473331622093625</v>
       </c>
       <c r="T32">
-        <v>1.218815224041264</v>
+        <v>1.232551732272914</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.085727382468706</v>
+        <v>4.921671660453587</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4058,22 +4058,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1828314119244601</v>
+        <v>0.1823229391252282</v>
       </c>
       <c r="C33">
-        <v>29.30485835591062</v>
+        <v>29.11508811095483</v>
       </c>
       <c r="D33">
-        <v>39.50375835591063</v>
+        <v>39.65088811095483</v>
       </c>
       <c r="E33">
-        <v>-14.0561</v>
+        <v>-13.7192</v>
       </c>
       <c r="F33">
-        <v>10.4439</v>
+        <v>10.7808</v>
       </c>
       <c r="G33">
         <v>0.245</v>
@@ -4094,28 +4094,28 @@
         <v>2.8425</v>
       </c>
       <c r="M33">
-        <v>0.57754767</v>
+        <v>0.59617824</v>
       </c>
       <c r="N33">
-        <v>2.26495233</v>
+        <v>2.24632176</v>
       </c>
       <c r="O33">
-        <v>0.6568361756999999</v>
+        <v>0.6514333103999999</v>
       </c>
       <c r="P33">
-        <v>1.6081161543</v>
+        <v>1.5948884496</v>
       </c>
       <c r="Q33">
-        <v>2.6781161543</v>
+        <v>2.6648884496</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2473331622093625</v>
+        <v>0.2496452634194533</v>
       </c>
       <c r="T33">
-        <v>1.232551732272914</v>
+        <v>1.246692255452555</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.921671660453587</v>
+        <v>4.767869421064412</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4140,22 +4140,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1823229391252282</v>
+        <v>0.1818144663259963</v>
       </c>
       <c r="C34">
-        <v>29.11508811095483</v>
+        <v>28.92641791778644</v>
       </c>
       <c r="D34">
-        <v>39.65088811095483</v>
+        <v>39.79911791778645</v>
       </c>
       <c r="E34">
-        <v>-13.7192</v>
+        <v>-13.3823</v>
       </c>
       <c r="F34">
-        <v>10.7808</v>
+        <v>11.1177</v>
       </c>
       <c r="G34">
         <v>0.245</v>
@@ -4176,28 +4176,28 @@
         <v>2.8425</v>
       </c>
       <c r="M34">
-        <v>0.59617824</v>
+        <v>0.61480881</v>
       </c>
       <c r="N34">
-        <v>2.24632176</v>
+        <v>2.22769119</v>
       </c>
       <c r="O34">
-        <v>0.6514333103999999</v>
+        <v>0.6460304450999999</v>
       </c>
       <c r="P34">
-        <v>1.5948884496</v>
+        <v>1.5816607449</v>
       </c>
       <c r="Q34">
-        <v>2.6648884496</v>
+        <v>2.6516607449</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2496452634194533</v>
+        <v>0.252026382576114</v>
       </c>
       <c r="T34">
-        <v>1.246692255452555</v>
+        <v>1.261254883801737</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.767869421064412</v>
+        <v>4.623388529517005</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4222,22 +4222,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1818144663259963</v>
+        <v>0.1819094935267645</v>
       </c>
       <c r="C35">
-        <v>28.92641791778644</v>
+        <v>28.56173147416101</v>
       </c>
       <c r="D35">
-        <v>39.79911791778645</v>
+        <v>39.77133147416101</v>
       </c>
       <c r="E35">
-        <v>-13.3823</v>
+        <v>-13.0454</v>
       </c>
       <c r="F35">
-        <v>11.1177</v>
+        <v>11.4546</v>
       </c>
       <c r="G35">
         <v>0.245</v>
@@ -4258,45 +4258,45 @@
         <v>2.8425</v>
       </c>
       <c r="M35">
-        <v>0.61480881</v>
+        <v>0.6620758799999999</v>
       </c>
       <c r="N35">
-        <v>2.22769119</v>
+        <v>2.18042412</v>
       </c>
       <c r="O35">
-        <v>0.6460304450999999</v>
+        <v>0.6323229947999999</v>
       </c>
       <c r="P35">
-        <v>1.5816607449</v>
+        <v>1.5481011252</v>
       </c>
       <c r="Q35">
-        <v>2.6516607449</v>
+        <v>2.618101125199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.252026382576114</v>
+        <v>0.2544796568587341</v>
       </c>
       <c r="T35">
-        <v>1.261254883801737</v>
+        <v>1.276258803919075</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.29</v>
       </c>
       <c r="W35">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.623388529517005</v>
+        <v>4.293314536696307</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4304,22 +4304,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1819094935267645</v>
+        <v>0.1814187707275326</v>
       </c>
       <c r="C36">
-        <v>28.56173147416101</v>
+        <v>28.36874001282038</v>
       </c>
       <c r="D36">
-        <v>39.77133147416101</v>
+        <v>39.91524001282038</v>
       </c>
       <c r="E36">
-        <v>-13.0454</v>
+        <v>-12.7085</v>
       </c>
       <c r="F36">
-        <v>11.4546</v>
+        <v>11.7915</v>
       </c>
       <c r="G36">
         <v>0.245</v>
@@ -4340,28 +4340,28 @@
         <v>2.8425</v>
       </c>
       <c r="M36">
-        <v>0.6620758799999999</v>
+        <v>0.6815487000000001</v>
       </c>
       <c r="N36">
-        <v>2.18042412</v>
+        <v>2.1609513</v>
       </c>
       <c r="O36">
-        <v>0.6323229947999999</v>
+        <v>0.6266758769999999</v>
       </c>
       <c r="P36">
-        <v>1.5481011252</v>
+        <v>1.534275423</v>
       </c>
       <c r="Q36">
-        <v>2.618101125199999</v>
+        <v>2.604275423</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2544796568587341</v>
+        <v>0.2570084165038963</v>
       </c>
       <c r="T36">
-        <v>1.276258803919075</v>
+        <v>1.291724383116948</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.293314536696307</v>
+        <v>4.170648407076412</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4386,22 +4386,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1814187707275326</v>
+        <v>0.1809280479283007</v>
       </c>
       <c r="C37">
-        <v>28.36874001282038</v>
+        <v>28.17679377047029</v>
       </c>
       <c r="D37">
-        <v>39.91524001282038</v>
+        <v>40.06019377047029</v>
       </c>
       <c r="E37">
-        <v>-12.7085</v>
+        <v>-12.3716</v>
       </c>
       <c r="F37">
-        <v>11.7915</v>
+        <v>12.1284</v>
       </c>
       <c r="G37">
         <v>0.245</v>
@@ -4422,28 +4422,28 @@
         <v>2.8425</v>
       </c>
       <c r="M37">
-        <v>0.6815487000000001</v>
+        <v>0.7010215200000001</v>
       </c>
       <c r="N37">
-        <v>2.1609513</v>
+        <v>2.14147848</v>
       </c>
       <c r="O37">
-        <v>0.6266758769999999</v>
+        <v>0.6210287591999999</v>
       </c>
       <c r="P37">
-        <v>1.534275423</v>
+        <v>1.5204497208</v>
       </c>
       <c r="Q37">
-        <v>2.604275423</v>
+        <v>2.5904497208</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2570084165038963</v>
+        <v>0.2596161998879699</v>
       </c>
       <c r="T37">
-        <v>1.291724383116948</v>
+        <v>1.307673261664754</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.170648407076412</v>
+        <v>4.054797062435402</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4468,22 +4468,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1809280479283007</v>
+        <v>0.1813567751290688</v>
       </c>
       <c r="C38">
-        <v>28.17679377047028</v>
+        <v>27.71319486721673</v>
       </c>
       <c r="D38">
-        <v>40.06019377047028</v>
+        <v>39.93349486721673</v>
       </c>
       <c r="E38">
-        <v>-12.3716</v>
+        <v>-12.0347</v>
       </c>
       <c r="F38">
-        <v>12.1284</v>
+        <v>12.4653</v>
       </c>
       <c r="G38">
         <v>0.245</v>
@@ -4504,45 +4504,45 @@
         <v>2.8425</v>
       </c>
       <c r="M38">
-        <v>0.70102152</v>
+        <v>0.76412289</v>
       </c>
       <c r="N38">
-        <v>2.14147848</v>
+        <v>2.07837711</v>
       </c>
       <c r="O38">
-        <v>0.6210287591999999</v>
+        <v>0.6027293618999999</v>
       </c>
       <c r="P38">
-        <v>1.5204497208</v>
+        <v>1.4756477481</v>
       </c>
       <c r="Q38">
-        <v>2.5904497208</v>
+        <v>2.5456477481</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2596161998879699</v>
+        <v>0.262306770046141</v>
       </c>
       <c r="T38">
-        <v>1.307673261664754</v>
+        <v>1.324128453817252</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.29</v>
       </c>
       <c r="W38">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.054797062435402</v>
+        <v>3.719951381118814</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4550,22 +4550,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1813567751290688</v>
+        <v>0.180890902329837</v>
       </c>
       <c r="C39">
-        <v>27.71319486721673</v>
+        <v>27.51400901906597</v>
       </c>
       <c r="D39">
-        <v>39.93349486721673</v>
+        <v>40.07120901906597</v>
       </c>
       <c r="E39">
-        <v>-12.0347</v>
+        <v>-11.6978</v>
       </c>
       <c r="F39">
-        <v>12.4653</v>
+        <v>12.8022</v>
       </c>
       <c r="G39">
         <v>0.245</v>
@@ -4586,28 +4586,28 @@
         <v>2.8425</v>
       </c>
       <c r="M39">
-        <v>0.76412289</v>
+        <v>0.78477486</v>
       </c>
       <c r="N39">
-        <v>2.07837711</v>
+        <v>2.05772514</v>
       </c>
       <c r="O39">
-        <v>0.6027293618999999</v>
+        <v>0.5967402905999999</v>
       </c>
       <c r="P39">
-        <v>1.4756477481</v>
+        <v>1.4609848494</v>
       </c>
       <c r="Q39">
-        <v>2.5456477481</v>
+        <v>2.530984849399999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.262306770046141</v>
+        <v>0.2650841327900596</v>
       </c>
       <c r="T39">
-        <v>1.324128453817252</v>
+        <v>1.341114458619831</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.719951381118814</v>
+        <v>3.622057923720951</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4632,22 +4632,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.180890902329837</v>
+        <v>0.1804250295306051</v>
       </c>
       <c r="C40">
-        <v>27.51400901906597</v>
+        <v>27.31577629646161</v>
       </c>
       <c r="D40">
-        <v>40.07120901906597</v>
+        <v>40.20987629646162</v>
       </c>
       <c r="E40">
-        <v>-11.6978</v>
+        <v>-11.3609</v>
       </c>
       <c r="F40">
-        <v>12.8022</v>
+        <v>13.1391</v>
       </c>
       <c r="G40">
         <v>0.245</v>
@@ -4668,28 +4668,28 @@
         <v>2.8425</v>
       </c>
       <c r="M40">
-        <v>0.78477486</v>
+        <v>0.8054268299999999</v>
       </c>
       <c r="N40">
-        <v>2.05772514</v>
+        <v>2.03707317</v>
       </c>
       <c r="O40">
-        <v>0.5967402905999999</v>
+        <v>0.5907512192999999</v>
       </c>
       <c r="P40">
-        <v>1.4609848494</v>
+        <v>1.4463219507</v>
       </c>
       <c r="Q40">
-        <v>2.530984849399999</v>
+        <v>2.5163219507</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2650841327900596</v>
+        <v>0.2679525566075493</v>
       </c>
       <c r="T40">
-        <v>1.341114458619831</v>
+        <v>1.358657381612658</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.622057923720951</v>
+        <v>3.529184643625542</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1804250295306051</v>
+        <v>0.1807543567313732</v>
       </c>
       <c r="C41">
-        <v>27.31577629646161</v>
+        <v>26.88075270619986</v>
       </c>
       <c r="D41">
-        <v>40.20987629646162</v>
+        <v>40.11175270619987</v>
       </c>
       <c r="E41">
-        <v>-11.3609</v>
+        <v>-11.024</v>
       </c>
       <c r="F41">
-        <v>13.1391</v>
+        <v>13.476</v>
       </c>
       <c r="G41">
         <v>0.245</v>
@@ -4750,45 +4750,45 @@
         <v>2.8425</v>
       </c>
       <c r="M41">
-        <v>0.8054268299999999</v>
+        <v>0.8638116</v>
       </c>
       <c r="N41">
-        <v>2.03707317</v>
+        <v>1.9786884</v>
       </c>
       <c r="O41">
-        <v>0.5907512192999999</v>
+        <v>0.5738196359999999</v>
       </c>
       <c r="P41">
-        <v>1.4463219507</v>
+        <v>1.404868764</v>
       </c>
       <c r="Q41">
-        <v>2.5163219507</v>
+        <v>2.474868764</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2679525566075493</v>
+        <v>0.2709165945522887</v>
       </c>
       <c r="T41">
-        <v>1.358657381612658</v>
+        <v>1.376785068705246</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.29</v>
       </c>
       <c r="W41">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.529184643625542</v>
+        <v>3.290648099655063</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4796,22 +4796,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1807543567313732</v>
+        <v>0.1803083639321413</v>
       </c>
       <c r="C42">
-        <v>26.88075270619986</v>
+        <v>26.67685226361445</v>
       </c>
       <c r="D42">
-        <v>40.11175270619987</v>
+        <v>40.24475226361445</v>
       </c>
       <c r="E42">
-        <v>-11.024</v>
+        <v>-10.6871</v>
       </c>
       <c r="F42">
-        <v>13.476</v>
+        <v>13.8129</v>
       </c>
       <c r="G42">
         <v>0.245</v>
@@ -4832,28 +4832,28 @@
         <v>2.8425</v>
       </c>
       <c r="M42">
-        <v>0.8638116</v>
+        <v>0.8854068900000001</v>
       </c>
       <c r="N42">
-        <v>1.9786884</v>
+        <v>1.95709311</v>
       </c>
       <c r="O42">
-        <v>0.5738196359999999</v>
+        <v>0.5675570018999999</v>
       </c>
       <c r="P42">
-        <v>1.404868764</v>
+        <v>1.3895361081</v>
       </c>
       <c r="Q42">
-        <v>2.474868764</v>
+        <v>2.4595361081</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2709165945522887</v>
+        <v>0.2739811083595616</v>
       </c>
       <c r="T42">
-        <v>1.376785068705246</v>
+        <v>1.39552725366538</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.290648099655063</v>
+        <v>3.210388389907379</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1803083639321413</v>
+        <v>0.1798623711329094</v>
       </c>
       <c r="C43">
-        <v>26.67685226361445</v>
+        <v>26.47383673518366</v>
       </c>
       <c r="D43">
-        <v>40.24475226361445</v>
+        <v>40.37863673518366</v>
       </c>
       <c r="E43">
-        <v>-10.6871</v>
+        <v>-10.3502</v>
       </c>
       <c r="F43">
-        <v>13.8129</v>
+        <v>14.1498</v>
       </c>
       <c r="G43">
         <v>0.245</v>
@@ -4914,28 +4914,28 @@
         <v>2.8425</v>
       </c>
       <c r="M43">
-        <v>0.8854068900000001</v>
+        <v>0.9070021800000001</v>
       </c>
       <c r="N43">
-        <v>1.95709311</v>
+        <v>1.93549782</v>
       </c>
       <c r="O43">
-        <v>0.5675570018999999</v>
+        <v>0.5612943677999999</v>
       </c>
       <c r="P43">
-        <v>1.3895361081</v>
+        <v>1.3742034522</v>
       </c>
       <c r="Q43">
-        <v>2.4595361081</v>
+        <v>2.4442034522</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2739811083595616</v>
+        <v>0.2771512950567404</v>
       </c>
       <c r="T43">
-        <v>1.39552725366538</v>
+        <v>1.414915720865518</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.210388389907379</v>
+        <v>3.13395057110006</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1798623711329095</v>
+        <v>0.1794163783336776</v>
       </c>
       <c r="C44">
-        <v>26.47383673518365</v>
+        <v>26.27171498206683</v>
       </c>
       <c r="D44">
-        <v>40.37863673518365</v>
+        <v>40.51341498206683</v>
       </c>
       <c r="E44">
-        <v>-10.3502</v>
+        <v>-10.0133</v>
       </c>
       <c r="F44">
-        <v>14.1498</v>
+        <v>14.4867</v>
       </c>
       <c r="G44">
         <v>0.245</v>
@@ -4996,28 +4996,28 @@
         <v>2.8425</v>
       </c>
       <c r="M44">
-        <v>0.90700218</v>
+        <v>0.92859747</v>
       </c>
       <c r="N44">
-        <v>1.93549782</v>
+        <v>1.91390253</v>
       </c>
       <c r="O44">
-        <v>0.5612943677999999</v>
+        <v>0.5550317336999998</v>
       </c>
       <c r="P44">
-        <v>1.3742034522</v>
+        <v>1.3588707963</v>
       </c>
       <c r="Q44">
-        <v>2.4442034522</v>
+        <v>2.4288707963</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2771512950567404</v>
+        <v>0.2804327163748729</v>
       </c>
       <c r="T44">
-        <v>1.414915720865518</v>
+        <v>1.434984485160398</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.13395057110006</v>
+        <v>3.061067999679128</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5042,22 +5042,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1794163783336776</v>
+        <v>0.1814071055344457</v>
       </c>
       <c r="C45">
-        <v>26.27171498206683</v>
+        <v>25.34007360120076</v>
       </c>
       <c r="D45">
-        <v>40.51341498206683</v>
+        <v>39.91867360120077</v>
       </c>
       <c r="E45">
-        <v>-10.0133</v>
+        <v>-9.676400000000001</v>
       </c>
       <c r="F45">
-        <v>14.4867</v>
+        <v>14.8236</v>
       </c>
       <c r="G45">
         <v>0.245</v>
@@ -5078,45 +5078,45 @@
         <v>2.8425</v>
       </c>
       <c r="M45">
-        <v>0.92859747</v>
+        <v>1.06581684</v>
       </c>
       <c r="N45">
-        <v>1.91390253</v>
+        <v>1.77668316</v>
       </c>
       <c r="O45">
-        <v>0.5550317336999998</v>
+        <v>0.5152381163999998</v>
       </c>
       <c r="P45">
-        <v>1.3588707963</v>
+        <v>1.2614450436</v>
       </c>
       <c r="Q45">
-        <v>2.4288707963</v>
+        <v>2.3314450436</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2804327163748729</v>
+        <v>0.2838313313115101</v>
       </c>
       <c r="T45">
-        <v>1.434984485160398</v>
+        <v>1.455769991037237</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.29</v>
       </c>
       <c r="W45">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.061067999679128</v>
+        <v>2.666968557186617</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5124,22 +5124,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1814071055344457</v>
+        <v>0.1810164927352138</v>
       </c>
       <c r="C46">
-        <v>25.34007360120076</v>
+        <v>25.11849048689697</v>
       </c>
       <c r="D46">
-        <v>39.91867360120077</v>
+        <v>40.03399048689697</v>
       </c>
       <c r="E46">
-        <v>-9.676400000000001</v>
+        <v>-9.339500000000001</v>
       </c>
       <c r="F46">
-        <v>14.8236</v>
+        <v>15.1605</v>
       </c>
       <c r="G46">
         <v>0.245</v>
@@ -5160,28 +5160,28 @@
         <v>2.8425</v>
       </c>
       <c r="M46">
-        <v>1.06581684</v>
+        <v>1.09003995</v>
       </c>
       <c r="N46">
-        <v>1.77668316</v>
+        <v>1.75246005</v>
       </c>
       <c r="O46">
-        <v>0.5152381163999998</v>
+        <v>0.5082134144999999</v>
       </c>
       <c r="P46">
-        <v>1.2614450436</v>
+        <v>1.2442466355</v>
       </c>
       <c r="Q46">
-        <v>2.3314450436</v>
+        <v>2.3142466355</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2838313313115101</v>
+        <v>0.2873535322458433</v>
       </c>
       <c r="T46">
-        <v>1.455769991037237</v>
+        <v>1.477311333491417</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.666968557186617</v>
+        <v>2.607702589249137</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5206,22 +5206,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1810164927352138</v>
+        <v>0.1806258799359819</v>
       </c>
       <c r="C47">
-        <v>25.11849048689697</v>
+        <v>24.89757555664718</v>
       </c>
       <c r="D47">
-        <v>40.03399048689697</v>
+        <v>40.14997555664718</v>
       </c>
       <c r="E47">
-        <v>-9.339500000000001</v>
+        <v>-9.002600000000001</v>
       </c>
       <c r="F47">
-        <v>15.1605</v>
+        <v>15.4974</v>
       </c>
       <c r="G47">
         <v>0.245</v>
@@ -5242,28 +5242,28 @@
         <v>2.8425</v>
       </c>
       <c r="M47">
-        <v>1.09003995</v>
+        <v>1.11426306</v>
       </c>
       <c r="N47">
-        <v>1.75246005</v>
+        <v>1.72823694</v>
       </c>
       <c r="O47">
-        <v>0.5082134144999999</v>
+        <v>0.5011887125999999</v>
       </c>
       <c r="P47">
-        <v>1.2442466355</v>
+        <v>1.2270482274</v>
       </c>
       <c r="Q47">
-        <v>2.3142466355</v>
+        <v>2.297048227399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2873535322458433</v>
+        <v>0.2910061850666332</v>
       </c>
       <c r="T47">
-        <v>1.477311333491417</v>
+        <v>1.4996505034439</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.607702589249137</v>
+        <v>2.551013402526329</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5288,22 +5288,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1806258799359819</v>
+        <v>0.18153669713675</v>
       </c>
       <c r="C48">
-        <v>24.89757555664718</v>
+        <v>24.2912621325783</v>
       </c>
       <c r="D48">
-        <v>40.14997555664718</v>
+        <v>39.8805621325783</v>
       </c>
       <c r="E48">
-        <v>-9.002600000000001</v>
+        <v>-8.665699999999999</v>
       </c>
       <c r="F48">
-        <v>15.4974</v>
+        <v>15.8343</v>
       </c>
       <c r="G48">
         <v>0.245</v>
@@ -5324,45 +5324,45 @@
         <v>2.8425</v>
       </c>
       <c r="M48">
-        <v>1.11426306</v>
+        <v>1.20023994</v>
       </c>
       <c r="N48">
-        <v>1.72823694</v>
+        <v>1.64226006</v>
       </c>
       <c r="O48">
-        <v>0.5011887125999999</v>
+        <v>0.4762554173999999</v>
       </c>
       <c r="P48">
-        <v>1.2270482274</v>
+        <v>1.1660046426</v>
       </c>
       <c r="Q48">
-        <v>2.297048227399999</v>
+        <v>2.2360046426</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2910061850666332</v>
+        <v>0.2947966738429246</v>
       </c>
       <c r="T48">
-        <v>1.4996505034439</v>
+        <v>1.522832660941758</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.29</v>
       </c>
       <c r="W48">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.551013402526329</v>
+        <v>2.368276463121199</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5370,22 +5370,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.18153669713675</v>
+        <v>0.1811737743375182</v>
       </c>
       <c r="C49">
-        <v>24.2912621325783</v>
+        <v>24.06127770994861</v>
       </c>
       <c r="D49">
-        <v>39.8805621325783</v>
+        <v>39.98747770994861</v>
       </c>
       <c r="E49">
-        <v>-8.665699999999999</v>
+        <v>-8.328800000000001</v>
       </c>
       <c r="F49">
-        <v>15.8343</v>
+        <v>16.1712</v>
       </c>
       <c r="G49">
         <v>0.245</v>
@@ -5406,28 +5406,28 @@
         <v>2.8425</v>
       </c>
       <c r="M49">
-        <v>1.20023994</v>
+        <v>1.22577696</v>
       </c>
       <c r="N49">
-        <v>1.64226006</v>
+        <v>1.61672304</v>
       </c>
       <c r="O49">
-        <v>0.4762554173999999</v>
+        <v>0.4688496816</v>
       </c>
       <c r="P49">
-        <v>1.1660046426</v>
+        <v>1.1478733584</v>
       </c>
       <c r="Q49">
-        <v>2.2360046426</v>
+        <v>2.2178733584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2947966738429246</v>
+        <v>0.2987329506490734</v>
       </c>
       <c r="T49">
-        <v>1.522832660941758</v>
+        <v>1.546906439881843</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.368276463121199</v>
+        <v>2.318937370139508</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5452,22 +5452,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1811737743375182</v>
+        <v>0.1808108515382863</v>
       </c>
       <c r="C50">
-        <v>24.06127770994862</v>
+        <v>23.83186808705065</v>
       </c>
       <c r="D50">
-        <v>39.98747770994862</v>
+        <v>40.09496808705065</v>
       </c>
       <c r="E50">
-        <v>-8.328800000000001</v>
+        <v>-7.991900000000001</v>
       </c>
       <c r="F50">
-        <v>16.1712</v>
+        <v>16.5081</v>
       </c>
       <c r="G50">
         <v>0.245</v>
@@ -5488,28 +5488,28 @@
         <v>2.8425</v>
       </c>
       <c r="M50">
-        <v>1.22577696</v>
+        <v>1.25131398</v>
       </c>
       <c r="N50">
-        <v>1.61672304</v>
+        <v>1.59118602</v>
       </c>
       <c r="O50">
-        <v>0.4688496816</v>
+        <v>0.4614439457999999</v>
       </c>
       <c r="P50">
-        <v>1.1478733584</v>
+        <v>1.1297420742</v>
       </c>
       <c r="Q50">
-        <v>2.2178733584</v>
+        <v>2.1997420742</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2987329506490734</v>
+        <v>0.3028235912515417</v>
       </c>
       <c r="T50">
-        <v>1.546906439881843</v>
+        <v>1.571924288584284</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.318937370139508</v>
+        <v>2.27161211768768</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5534,22 +5534,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1808108515382863</v>
+        <v>0.1804479287390544</v>
       </c>
       <c r="C51">
-        <v>23.83186808705065</v>
+        <v>23.60303791173741</v>
       </c>
       <c r="D51">
-        <v>40.09496808705065</v>
+        <v>40.20303791173741</v>
       </c>
       <c r="E51">
-        <v>-7.991900000000001</v>
+        <v>-7.655000000000001</v>
       </c>
       <c r="F51">
-        <v>16.5081</v>
+        <v>16.845</v>
       </c>
       <c r="G51">
         <v>0.245</v>
@@ -5570,28 +5570,28 @@
         <v>2.8425</v>
       </c>
       <c r="M51">
-        <v>1.25131398</v>
+        <v>1.276851</v>
       </c>
       <c r="N51">
-        <v>1.59118602</v>
+        <v>1.565649</v>
       </c>
       <c r="O51">
-        <v>0.4614439457999999</v>
+        <v>0.4540382099999999</v>
       </c>
       <c r="P51">
-        <v>1.1297420742</v>
+        <v>1.11161079</v>
       </c>
       <c r="Q51">
-        <v>2.1997420742</v>
+        <v>2.18161079</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3028235912515417</v>
+        <v>0.3070778574781088</v>
       </c>
       <c r="T51">
-        <v>1.571924288584284</v>
+        <v>1.597942851234822</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.27161211768768</v>
+        <v>2.226179875333927</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5616,22 +5616,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1804479287390544</v>
+        <v>0.1800850059398225</v>
       </c>
       <c r="C52">
-        <v>23.60303791173741</v>
+        <v>23.37479188210767</v>
       </c>
       <c r="D52">
-        <v>40.20303791173741</v>
+        <v>40.31169188210767</v>
       </c>
       <c r="E52">
-        <v>-7.655000000000001</v>
+        <v>-7.318100000000001</v>
       </c>
       <c r="F52">
-        <v>16.845</v>
+        <v>17.1819</v>
       </c>
       <c r="G52">
         <v>0.245</v>
@@ -5652,28 +5652,28 @@
         <v>2.8425</v>
       </c>
       <c r="M52">
-        <v>1.276851</v>
+        <v>1.30238802</v>
       </c>
       <c r="N52">
-        <v>1.565649</v>
+        <v>1.54011198</v>
       </c>
       <c r="O52">
-        <v>0.4540382099999999</v>
+        <v>0.4466324741999999</v>
       </c>
       <c r="P52">
-        <v>1.11161079</v>
+        <v>1.0934795058</v>
       </c>
       <c r="Q52">
-        <v>2.18161079</v>
+        <v>2.1634795058</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3070778574781088</v>
+        <v>0.3115057672241276</v>
       </c>
       <c r="T52">
-        <v>1.597942851234822</v>
+        <v>1.625023396034362</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.226179875333927</v>
+        <v>2.182529289543066</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5698,22 +5698,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1800850059398225</v>
+        <v>0.1797220831405907</v>
       </c>
       <c r="C53">
-        <v>23.37479188210767</v>
+        <v>23.14713474718667</v>
       </c>
       <c r="D53">
-        <v>40.31169188210767</v>
+        <v>40.42093474718667</v>
       </c>
       <c r="E53">
-        <v>-7.318100000000001</v>
+        <v>-6.981200000000001</v>
       </c>
       <c r="F53">
-        <v>17.1819</v>
+        <v>17.5188</v>
       </c>
       <c r="G53">
         <v>0.245</v>
@@ -5734,28 +5734,28 @@
         <v>2.8425</v>
       </c>
       <c r="M53">
-        <v>1.30238802</v>
+        <v>1.32792504</v>
       </c>
       <c r="N53">
-        <v>1.54011198</v>
+        <v>1.51457496</v>
       </c>
       <c r="O53">
-        <v>0.4466324741999999</v>
+        <v>0.4392267383999999</v>
       </c>
       <c r="P53">
-        <v>1.0934795058</v>
+        <v>1.0753482216</v>
       </c>
       <c r="Q53">
-        <v>2.1634795058</v>
+        <v>2.1453482216</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3115057672241276</v>
+        <v>0.3161181732095639</v>
       </c>
       <c r="T53">
-        <v>1.625023396034362</v>
+        <v>1.653232296867216</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.182529289543066</v>
+        <v>2.140557572436468</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5780,22 +5780,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1797220831405907</v>
+        <v>0.1793591603413588</v>
       </c>
       <c r="C54">
-        <v>23.14713474718667</v>
+        <v>22.9200713076182</v>
       </c>
       <c r="D54">
-        <v>40.42093474718667</v>
+        <v>40.5307713076182</v>
       </c>
       <c r="E54">
-        <v>-6.981200000000001</v>
+        <v>-6.644300000000001</v>
       </c>
       <c r="F54">
-        <v>17.5188</v>
+        <v>17.8557</v>
       </c>
       <c r="G54">
         <v>0.245</v>
@@ -5816,28 +5816,28 @@
         <v>2.8425</v>
       </c>
       <c r="M54">
-        <v>1.32792504</v>
+        <v>1.35346206</v>
       </c>
       <c r="N54">
-        <v>1.51457496</v>
+        <v>1.48903794</v>
       </c>
       <c r="O54">
-        <v>0.4392267383999999</v>
+        <v>0.4318210025999999</v>
       </c>
       <c r="P54">
-        <v>1.0753482216</v>
+        <v>1.0572169374</v>
       </c>
       <c r="Q54">
-        <v>2.1453482216</v>
+        <v>2.1272169374</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3161181732095639</v>
+        <v>0.320926851790125</v>
       </c>
       <c r="T54">
-        <v>1.653232296867216</v>
+        <v>1.682641576458915</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.140557572436468</v>
+        <v>2.100169693711252</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5862,22 +5862,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1793591603413588</v>
+        <v>0.1789962375421269</v>
       </c>
       <c r="C55">
-        <v>22.9200713076182</v>
+        <v>22.69360641636769</v>
       </c>
       <c r="D55">
-        <v>40.5307713076182</v>
+        <v>40.64120641636769</v>
       </c>
       <c r="E55">
-        <v>-6.644300000000001</v>
+        <v>-6.307400000000001</v>
       </c>
       <c r="F55">
-        <v>17.8557</v>
+        <v>18.1926</v>
       </c>
       <c r="G55">
         <v>0.245</v>
@@ -5898,28 +5898,28 @@
         <v>2.8425</v>
       </c>
       <c r="M55">
-        <v>1.35346206</v>
+        <v>1.37899908</v>
       </c>
       <c r="N55">
-        <v>1.48903794</v>
+        <v>1.46350092</v>
       </c>
       <c r="O55">
-        <v>0.4318210025999999</v>
+        <v>0.4244152667999999</v>
       </c>
       <c r="P55">
-        <v>1.0572169374</v>
+        <v>1.0390856532</v>
       </c>
       <c r="Q55">
-        <v>2.1272169374</v>
+        <v>2.1090856532</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.320926851790125</v>
+        <v>0.3259446033524497</v>
       </c>
       <c r="T55">
-        <v>1.682641576458915</v>
+        <v>1.713329520380688</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.100169693711252</v>
+        <v>2.061277662346229</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5944,22 +5944,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1789962375421269</v>
+        <v>0.178633314742895</v>
       </c>
       <c r="C56">
-        <v>22.69360641636769</v>
+        <v>22.46774497943702</v>
       </c>
       <c r="D56">
-        <v>40.64120641636769</v>
+        <v>40.75224497943702</v>
       </c>
       <c r="E56">
-        <v>-6.307400000000001</v>
+        <v>-5.970500000000001</v>
       </c>
       <c r="F56">
-        <v>18.1926</v>
+        <v>18.5295</v>
       </c>
       <c r="G56">
         <v>0.245</v>
@@ -5980,28 +5980,28 @@
         <v>2.8425</v>
       </c>
       <c r="M56">
-        <v>1.37899908</v>
+        <v>1.4045361</v>
       </c>
       <c r="N56">
-        <v>1.46350092</v>
+        <v>1.4379639</v>
       </c>
       <c r="O56">
-        <v>0.4244152667999999</v>
+        <v>0.4170095309999999</v>
       </c>
       <c r="P56">
-        <v>1.0390856532</v>
+        <v>1.020954369</v>
       </c>
       <c r="Q56">
-        <v>2.1090856532</v>
+        <v>2.090954368999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3259446033524497</v>
+        <v>0.3311853660953223</v>
       </c>
       <c r="T56">
-        <v>1.713329520380688</v>
+        <v>1.745381372921206</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.061277662346229</v>
+        <v>2.023799886667206</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6026,22 +6026,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.178633314742895</v>
+        <v>0.1839163119436631</v>
       </c>
       <c r="C57">
-        <v>22.46774497943702</v>
+        <v>20.57205736686887</v>
       </c>
       <c r="D57">
-        <v>40.75224497943702</v>
+        <v>39.19345736686888</v>
       </c>
       <c r="E57">
-        <v>-5.970500000000001</v>
+        <v>-5.633599999999998</v>
       </c>
       <c r="F57">
-        <v>18.5295</v>
+        <v>18.8664</v>
       </c>
       <c r="G57">
         <v>0.245</v>
@@ -6062,45 +6062,45 @@
         <v>2.8425</v>
       </c>
       <c r="M57">
-        <v>1.4045361</v>
+        <v>1.697976</v>
       </c>
       <c r="N57">
-        <v>1.4379639</v>
+        <v>1.144524</v>
       </c>
       <c r="O57">
-        <v>0.4170095309999999</v>
+        <v>0.3319119599999999</v>
       </c>
       <c r="P57">
-        <v>1.020954369</v>
+        <v>0.8126120399999998</v>
       </c>
       <c r="Q57">
-        <v>2.090954368999999</v>
+        <v>1.88261204</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3311853660953223</v>
+        <v>0.3366643453265071</v>
       </c>
       <c r="T57">
-        <v>1.745381372921206</v>
+        <v>1.77889012784993</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.29</v>
       </c>
       <c r="W57">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.023799886667206</v>
+        <v>1.674051930062615</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6108,22 +6108,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1839163119436631</v>
+        <v>0.1836542091444313</v>
       </c>
       <c r="C58">
-        <v>20.57205736686887</v>
+        <v>20.30967605549786</v>
       </c>
       <c r="D58">
-        <v>39.19345736686888</v>
+        <v>39.26797605549787</v>
       </c>
       <c r="E58">
-        <v>-5.633599999999998</v>
+        <v>-5.296699999999998</v>
       </c>
       <c r="F58">
-        <v>18.8664</v>
+        <v>19.2033</v>
       </c>
       <c r="G58">
         <v>0.245</v>
@@ -6144,28 +6144,28 @@
         <v>2.8425</v>
       </c>
       <c r="M58">
-        <v>1.697976</v>
+        <v>1.728297</v>
       </c>
       <c r="N58">
-        <v>1.144524</v>
+        <v>1.114203</v>
       </c>
       <c r="O58">
-        <v>0.3319119599999999</v>
+        <v>0.3231188699999999</v>
       </c>
       <c r="P58">
-        <v>0.8126120399999998</v>
+        <v>0.7910841299999998</v>
       </c>
       <c r="Q58">
-        <v>1.88261204</v>
+        <v>1.86108413</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3366643453265071</v>
+        <v>0.3423981608010029</v>
       </c>
       <c r="T58">
-        <v>1.77889012784993</v>
+        <v>1.813957429519524</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.674051930062615</v>
+        <v>1.644682597956254</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6190,22 +6190,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1836542091444313</v>
+        <v>0.1833921063451994</v>
       </c>
       <c r="C59">
-        <v>20.30967605549786</v>
+        <v>20.04757864932178</v>
       </c>
       <c r="D59">
-        <v>39.26797605549787</v>
+        <v>39.34277864932179</v>
       </c>
       <c r="E59">
-        <v>-5.296699999999998</v>
+        <v>-4.959799999999998</v>
       </c>
       <c r="F59">
-        <v>19.2033</v>
+        <v>19.5402</v>
       </c>
       <c r="G59">
         <v>0.245</v>
@@ -6226,28 +6226,28 @@
         <v>2.8425</v>
       </c>
       <c r="M59">
-        <v>1.728297</v>
+        <v>1.758618</v>
       </c>
       <c r="N59">
-        <v>1.114203</v>
+        <v>1.083882</v>
       </c>
       <c r="O59">
-        <v>0.3231188699999999</v>
+        <v>0.3143257799999998</v>
       </c>
       <c r="P59">
-        <v>0.7910841299999998</v>
+        <v>0.7695562199999997</v>
       </c>
       <c r="Q59">
-        <v>1.86108413</v>
+        <v>1.83955622</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3423981608010029</v>
+        <v>0.3484050151076176</v>
       </c>
       <c r="T59">
-        <v>1.813957429519524</v>
+        <v>1.850694602697194</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.644682597956254</v>
+        <v>1.616326001439766</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6272,22 +6272,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1833921063451994</v>
+        <v>0.1831300035459675</v>
       </c>
       <c r="C60">
-        <v>20.04757864932179</v>
+        <v>19.78576677389243</v>
       </c>
       <c r="D60">
-        <v>39.34277864932179</v>
+        <v>39.41786677389243</v>
       </c>
       <c r="E60">
-        <v>-4.959800000000001</v>
+        <v>-4.622900000000001</v>
       </c>
       <c r="F60">
-        <v>19.5402</v>
+        <v>19.8771</v>
       </c>
       <c r="G60">
         <v>0.245</v>
@@ -6308,28 +6308,28 @@
         <v>2.8425</v>
       </c>
       <c r="M60">
-        <v>1.758618</v>
+        <v>1.788939</v>
       </c>
       <c r="N60">
-        <v>1.083882</v>
+        <v>1.053561</v>
       </c>
       <c r="O60">
-        <v>0.31432578</v>
+        <v>0.30553269</v>
       </c>
       <c r="P60">
-        <v>0.76955622</v>
+        <v>0.74802831</v>
       </c>
       <c r="Q60">
-        <v>1.83955622</v>
+        <v>1.81802831</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3484050151076175</v>
+        <v>0.3547048866974816</v>
       </c>
       <c r="T60">
-        <v>1.850694602697194</v>
+        <v>1.889223833103044</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.616326001439767</v>
+        <v>1.588930645483161</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6354,22 +6354,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1831300035459675</v>
+        <v>0.1828679007467356</v>
       </c>
       <c r="C61">
-        <v>19.78576677389243</v>
+        <v>19.52424206719525</v>
       </c>
       <c r="D61">
-        <v>39.41786677389243</v>
+        <v>39.49324206719525</v>
       </c>
       <c r="E61">
-        <v>-4.622900000000001</v>
+        <v>-4.286000000000001</v>
       </c>
       <c r="F61">
-        <v>19.8771</v>
+        <v>20.214</v>
       </c>
       <c r="G61">
         <v>0.245</v>
@@ -6390,28 +6390,28 @@
         <v>2.8425</v>
       </c>
       <c r="M61">
-        <v>1.788939</v>
+        <v>1.81926</v>
       </c>
       <c r="N61">
-        <v>1.053561</v>
+        <v>1.02324</v>
       </c>
       <c r="O61">
-        <v>0.30553269</v>
+        <v>0.2967395999999999</v>
       </c>
       <c r="P61">
-        <v>0.74802831</v>
+        <v>0.7265003999999999</v>
       </c>
       <c r="Q61">
-        <v>1.81802831</v>
+        <v>1.7965004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3547048866974816</v>
+        <v>0.361319751866839</v>
       </c>
       <c r="T61">
-        <v>1.889223833103044</v>
+        <v>1.929679525029185</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.588930645483161</v>
+        <v>1.562448468058441</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6436,22 +6436,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1828679007467356</v>
+        <v>0.1826057979475037</v>
       </c>
       <c r="C62">
-        <v>19.52424206719525</v>
+        <v>19.26300617976837</v>
       </c>
       <c r="D62">
-        <v>39.49324206719525</v>
+        <v>39.56890617976837</v>
       </c>
       <c r="E62">
-        <v>-4.286000000000001</v>
+        <v>-3.949100000000001</v>
       </c>
       <c r="F62">
-        <v>20.214</v>
+        <v>20.5509</v>
       </c>
       <c r="G62">
         <v>0.245</v>
@@ -6472,28 +6472,28 @@
         <v>2.8425</v>
       </c>
       <c r="M62">
-        <v>1.81926</v>
+        <v>1.849581</v>
       </c>
       <c r="N62">
-        <v>1.02324</v>
+        <v>0.9929190000000001</v>
       </c>
       <c r="O62">
-        <v>0.2967395999999999</v>
+        <v>0.28794651</v>
       </c>
       <c r="P62">
-        <v>0.7265003999999999</v>
+        <v>0.7049724900000001</v>
       </c>
       <c r="Q62">
-        <v>1.7965004</v>
+        <v>1.77497249</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.361319751866839</v>
+        <v>0.3682738408910352</v>
       </c>
       <c r="T62">
-        <v>1.929679525029185</v>
+        <v>1.972209867823335</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.562448468058441</v>
+        <v>1.536834558746008</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6518,22 +6518,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1826057979475037</v>
+        <v>0.1823436951482718</v>
       </c>
       <c r="C63">
-        <v>19.26300617976837</v>
+        <v>19.00206077482308</v>
       </c>
       <c r="D63">
-        <v>39.56890617976837</v>
+        <v>39.64486077482308</v>
       </c>
       <c r="E63">
-        <v>-3.949100000000001</v>
+        <v>-3.612200000000001</v>
       </c>
       <c r="F63">
-        <v>20.5509</v>
+        <v>20.8878</v>
       </c>
       <c r="G63">
         <v>0.245</v>
@@ -6554,28 +6554,28 @@
         <v>2.8425</v>
       </c>
       <c r="M63">
-        <v>1.849581</v>
+        <v>1.879902</v>
       </c>
       <c r="N63">
-        <v>0.9929190000000001</v>
+        <v>0.9625980000000001</v>
       </c>
       <c r="O63">
-        <v>0.28794651</v>
+        <v>0.27915342</v>
       </c>
       <c r="P63">
-        <v>0.7049724900000001</v>
+        <v>0.6834445800000001</v>
       </c>
       <c r="Q63">
-        <v>1.77497249</v>
+        <v>1.75344458</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3682738408910352</v>
+        <v>0.3755939346007153</v>
       </c>
       <c r="T63">
-        <v>1.972209867823335</v>
+        <v>2.016978649711913</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.536834558746008</v>
+        <v>1.512046904572685</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6600,22 +6600,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1823436951482718</v>
+        <v>0.2122891191159064</v>
       </c>
       <c r="C64">
-        <v>19.00206077482308</v>
+        <v>11.53447157216456</v>
       </c>
       <c r="D64">
-        <v>39.64486077482308</v>
+        <v>32.51417157216456</v>
       </c>
       <c r="E64">
-        <v>-3.612200000000001</v>
+        <v>-3.275300000000001</v>
       </c>
       <c r="F64">
-        <v>20.8878</v>
+        <v>21.2247</v>
       </c>
       <c r="G64">
         <v>0.245</v>
@@ -6636,45 +6636,45 @@
         <v>2.8425</v>
       </c>
       <c r="M64">
-        <v>1.879902</v>
+        <v>3.11578596</v>
       </c>
       <c r="N64">
-        <v>0.9625980000000001</v>
+        <v>-0.2732859600000004</v>
       </c>
       <c r="O64">
-        <v>0.27915342</v>
+        <v>-0.0792529284000001</v>
       </c>
       <c r="P64">
-        <v>0.6834445800000001</v>
+        <v>-0.1940330316000003</v>
       </c>
       <c r="Q64">
-        <v>1.75344458</v>
+        <v>0.8759669683999995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3755939346007153</v>
+        <v>0.3899271949343286</v>
       </c>
       <c r="T64">
-        <v>2.016978649711913</v>
+        <v>2.104639085640372</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.29</v>
+        <v>0.2645640652415033</v>
       </c>
       <c r="W64">
-        <v>0.0639</v>
+        <v>0.1079619952225473</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.512046904572685</v>
+        <v>0.9122898801431147</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6682,22 +6682,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2122891191159064</v>
+        <v>0.2132991191159064</v>
       </c>
       <c r="C65">
-        <v>11.53447157216456</v>
+        <v>11.00151493938213</v>
       </c>
       <c r="D65">
-        <v>32.51417157216456</v>
+        <v>32.31811493938213</v>
       </c>
       <c r="E65">
-        <v>-3.275300000000001</v>
+        <v>-2.938400000000001</v>
       </c>
       <c r="F65">
-        <v>21.2247</v>
+        <v>21.5616</v>
       </c>
       <c r="G65">
         <v>0.245</v>
@@ -6718,37 +6718,37 @@
         <v>2.8425</v>
       </c>
       <c r="M65">
-        <v>3.11578596</v>
+        <v>3.16524288</v>
       </c>
       <c r="N65">
-        <v>-0.2732859600000004</v>
+        <v>-0.3227428800000003</v>
       </c>
       <c r="O65">
-        <v>-0.0792529284000001</v>
+        <v>-0.09359543520000008</v>
       </c>
       <c r="P65">
-        <v>-0.1940330316000003</v>
+        <v>-0.2291474448000002</v>
       </c>
       <c r="Q65">
-        <v>0.8759669683999995</v>
+        <v>0.8408525551999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3899271949343286</v>
+        <v>0.3994862836825044</v>
       </c>
       <c r="T65">
-        <v>2.104639085640372</v>
+        <v>2.163101282463716</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2645640652415033</v>
+        <v>0.2604302517221048</v>
       </c>
       <c r="W65">
-        <v>0.1079619952225473</v>
+        <v>0.108568839047195</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9122898801431147</v>
+        <v>0.8980353507658786</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6764,22 +6764,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2132991191159064</v>
+        <v>0.2143091191159064</v>
       </c>
       <c r="C66">
-        <v>11.00151493938213</v>
+        <v>10.47090853191867</v>
       </c>
       <c r="D66">
-        <v>32.31811493938213</v>
+        <v>32.12440853191867</v>
       </c>
       <c r="E66">
-        <v>-2.938400000000001</v>
+        <v>-2.601500000000001</v>
       </c>
       <c r="F66">
-        <v>21.5616</v>
+        <v>21.8985</v>
       </c>
       <c r="G66">
         <v>0.245</v>
@@ -6800,37 +6800,37 @@
         <v>2.8425</v>
       </c>
       <c r="M66">
-        <v>3.16524288</v>
+        <v>3.2146998</v>
       </c>
       <c r="N66">
-        <v>-0.3227428800000003</v>
+        <v>-0.3721998000000002</v>
       </c>
       <c r="O66">
-        <v>-0.09359543520000008</v>
+        <v>-0.1079379420000001</v>
       </c>
       <c r="P66">
-        <v>-0.2291474448000002</v>
+        <v>-0.2642618580000001</v>
       </c>
       <c r="Q66">
-        <v>0.8408525551999997</v>
+        <v>0.8057381419999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3994862836825044</v>
+        <v>0.4095916060734331</v>
       </c>
       <c r="T66">
-        <v>2.163101282463716</v>
+        <v>2.224904176248394</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2604302517221048</v>
+        <v>0.2564236324648416</v>
       </c>
       <c r="W66">
-        <v>0.108568839047195</v>
+        <v>0.1091570107541612</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8980353507658786</v>
+        <v>0.8842194222925575</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6846,22 +6846,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2143091191159064</v>
+        <v>0.2153191191159064</v>
       </c>
       <c r="C67">
-        <v>10.47090853191867</v>
+        <v>9.942610341635167</v>
       </c>
       <c r="D67">
-        <v>32.12440853191867</v>
+        <v>31.93301034163516</v>
       </c>
       <c r="E67">
-        <v>-2.601500000000001</v>
+        <v>-2.264600000000002</v>
       </c>
       <c r="F67">
-        <v>21.8985</v>
+        <v>22.2354</v>
       </c>
       <c r="G67">
         <v>0.245</v>
@@ -6882,37 +6882,37 @@
         <v>2.8425</v>
       </c>
       <c r="M67">
-        <v>3.2146998</v>
+        <v>3.26415672</v>
       </c>
       <c r="N67">
-        <v>-0.3721998000000002</v>
+        <v>-0.4216567200000001</v>
       </c>
       <c r="O67">
-        <v>-0.1079379420000001</v>
+        <v>-0.1222804488</v>
       </c>
       <c r="P67">
-        <v>-0.2642618580000001</v>
+        <v>-0.2993762712000001</v>
       </c>
       <c r="Q67">
-        <v>0.8057381419999997</v>
+        <v>0.7706237287999997</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4095916060734331</v>
+        <v>0.42029135919324</v>
       </c>
       <c r="T67">
-        <v>2.224904176248394</v>
+        <v>2.290342534373347</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2564236324648416</v>
+        <v>0.252538425912344</v>
       </c>
       <c r="W67">
-        <v>0.1091570107541612</v>
+        <v>0.1097273590760679</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8842194222925575</v>
+        <v>0.8708221583184278</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6928,22 +6928,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2153191191159064</v>
+        <v>0.2163291191159064</v>
       </c>
       <c r="C68">
-        <v>9.942610341635167</v>
+        <v>9.416579355606142</v>
       </c>
       <c r="D68">
-        <v>31.93301034163516</v>
+        <v>31.74387935560614</v>
       </c>
       <c r="E68">
-        <v>-2.264600000000002</v>
+        <v>-1.927700000000002</v>
       </c>
       <c r="F68">
-        <v>22.2354</v>
+        <v>22.5723</v>
       </c>
       <c r="G68">
         <v>0.245</v>
@@ -6964,37 +6964,37 @@
         <v>2.8425</v>
       </c>
       <c r="M68">
-        <v>3.26415672</v>
+        <v>3.31361364</v>
       </c>
       <c r="N68">
-        <v>-0.4216567200000001</v>
+        <v>-0.4711136400000004</v>
       </c>
       <c r="O68">
-        <v>-0.1222804488</v>
+        <v>-0.1366229556000001</v>
       </c>
       <c r="P68">
-        <v>-0.2993762712000001</v>
+        <v>-0.3344906844000003</v>
       </c>
       <c r="Q68">
-        <v>0.7706237287999997</v>
+        <v>0.7355093155999995</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.42029135919324</v>
+        <v>0.4316395821990957</v>
       </c>
       <c r="T68">
-        <v>2.290342534373347</v>
+        <v>2.359746853596781</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.252538425912344</v>
+        <v>0.2487691956748463</v>
       </c>
       <c r="W68">
-        <v>0.1097273590760679</v>
+        <v>0.1102806820749326</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8708221583184278</v>
+        <v>0.8578248126718839</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7010,22 +7010,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2163291191159064</v>
+        <v>0.2173391191159064</v>
       </c>
       <c r="C69">
-        <v>9.416579355606142</v>
+        <v>8.892775526821183</v>
       </c>
       <c r="D69">
-        <v>31.74387935560614</v>
+        <v>31.55697552682118</v>
       </c>
       <c r="E69">
-        <v>-1.927700000000002</v>
+        <v>-1.590800000000002</v>
       </c>
       <c r="F69">
-        <v>22.5723</v>
+        <v>22.9092</v>
       </c>
       <c r="G69">
         <v>0.245</v>
@@ -7046,37 +7046,37 @@
         <v>2.8425</v>
       </c>
       <c r="M69">
-        <v>3.31361364</v>
+        <v>3.36307056</v>
       </c>
       <c r="N69">
-        <v>-0.4711136400000004</v>
+        <v>-0.5205705600000003</v>
       </c>
       <c r="O69">
-        <v>-0.1366229556000001</v>
+        <v>-0.1509654624000001</v>
       </c>
       <c r="P69">
-        <v>-0.3344906844000003</v>
+        <v>-0.3696050976000003</v>
       </c>
       <c r="Q69">
-        <v>0.7355093155999995</v>
+        <v>0.7003949023999996</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4316395821990957</v>
+        <v>0.4436970691428175</v>
       </c>
       <c r="T69">
-        <v>2.359746853596781</v>
+        <v>2.433488942771681</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2487691956748463</v>
+        <v>0.2451108251502163</v>
       </c>
       <c r="W69">
-        <v>0.1102806820749326</v>
+        <v>0.1108177308679483</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8578248126718839</v>
+        <v>0.8452097418972975</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7092,22 +7092,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2173391191159064</v>
+        <v>0.2183491191159065</v>
       </c>
       <c r="C70">
-        <v>8.892775526821183</v>
+        <v>8.371159745915449</v>
       </c>
       <c r="D70">
-        <v>31.55697552682118</v>
+        <v>31.37225974591545</v>
       </c>
       <c r="E70">
-        <v>-1.590800000000002</v>
+        <v>-1.253899999999998</v>
       </c>
       <c r="F70">
-        <v>22.9092</v>
+        <v>23.2461</v>
       </c>
       <c r="G70">
         <v>0.245</v>
@@ -7128,37 +7128,37 @@
         <v>2.8425</v>
       </c>
       <c r="M70">
-        <v>3.36307056</v>
+        <v>3.412527480000001</v>
       </c>
       <c r="N70">
-        <v>-0.5205705600000003</v>
+        <v>-0.5700274800000007</v>
       </c>
       <c r="O70">
-        <v>-0.1509654624000001</v>
+        <v>-0.1653079692000002</v>
       </c>
       <c r="P70">
-        <v>-0.3696050976000003</v>
+        <v>-0.4047195108000005</v>
       </c>
       <c r="Q70">
-        <v>0.7003949023999996</v>
+        <v>0.6652804891999993</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4436970691428175</v>
+        <v>0.4565324584700053</v>
       </c>
       <c r="T70">
-        <v>2.433488942771681</v>
+        <v>2.511988586086897</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2451108251502163</v>
+        <v>0.2415584943509377</v>
       </c>
       <c r="W70">
-        <v>0.1108177308679483</v>
+        <v>0.1113392130292824</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8452097418972975</v>
+        <v>0.8329603253480612</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7174,22 +7174,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2183491191159065</v>
+        <v>0.2193591191159064</v>
       </c>
       <c r="C71">
-        <v>8.371159745915449</v>
+        <v>7.851693813887337</v>
       </c>
       <c r="D71">
-        <v>31.37225974591545</v>
+        <v>31.18969381388734</v>
       </c>
       <c r="E71">
-        <v>-1.253899999999998</v>
+        <v>-0.916999999999998</v>
       </c>
       <c r="F71">
-        <v>23.2461</v>
+        <v>23.583</v>
       </c>
       <c r="G71">
         <v>0.245</v>
@@ -7210,37 +7210,37 @@
         <v>2.8425</v>
       </c>
       <c r="M71">
-        <v>3.412527480000001</v>
+        <v>3.4619844</v>
       </c>
       <c r="N71">
-        <v>-0.5700274800000007</v>
+        <v>-0.6194844000000006</v>
       </c>
       <c r="O71">
-        <v>-0.1653079692000002</v>
+        <v>-0.1796504760000002</v>
       </c>
       <c r="P71">
-        <v>-0.4047195108000005</v>
+        <v>-0.4398339240000004</v>
       </c>
       <c r="Q71">
-        <v>0.6652804891999993</v>
+        <v>0.6301660759999994</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4565324584700053</v>
+        <v>0.4702235404190054</v>
       </c>
       <c r="T71">
-        <v>2.511988586086897</v>
+        <v>2.59572153895646</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2415584943509377</v>
+        <v>0.2381076587173529</v>
       </c>
       <c r="W71">
-        <v>0.1113392130292824</v>
+        <v>0.1118457957002926</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8329603253480612</v>
+        <v>0.8210608921288032</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7256,22 +7256,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2193591191159064</v>
+        <v>0.2203691191159064</v>
       </c>
       <c r="C72">
-        <v>7.851693813887337</v>
+        <v>7.334340415763069</v>
       </c>
       <c r="D72">
-        <v>31.18969381388734</v>
+        <v>31.00924041576307</v>
       </c>
       <c r="E72">
-        <v>-0.916999999999998</v>
+        <v>-0.5800999999999981</v>
       </c>
       <c r="F72">
-        <v>23.583</v>
+        <v>23.9199</v>
       </c>
       <c r="G72">
         <v>0.245</v>
@@ -7292,37 +7292,37 @@
         <v>2.8425</v>
       </c>
       <c r="M72">
-        <v>3.4619844</v>
+        <v>3.511441320000001</v>
       </c>
       <c r="N72">
-        <v>-0.6194844000000006</v>
+        <v>-0.6689413200000009</v>
       </c>
       <c r="O72">
-        <v>-0.1796504760000002</v>
+        <v>-0.1939929828000003</v>
       </c>
       <c r="P72">
-        <v>-0.4398339240000004</v>
+        <v>-0.4749483372000007</v>
       </c>
       <c r="Q72">
-        <v>0.6301660759999994</v>
+        <v>0.5950516627999991</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4702235404190054</v>
+        <v>0.4848588349162125</v>
       </c>
       <c r="T72">
-        <v>2.59572153895646</v>
+        <v>2.68522917823082</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2381076587173529</v>
+        <v>0.2347540297213339</v>
       </c>
       <c r="W72">
-        <v>0.1118457957002926</v>
+        <v>0.1123381084369082</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8210608921288032</v>
+        <v>0.8094966542114961</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7338,22 +7338,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2203691191159064</v>
+        <v>0.2671078161031929</v>
       </c>
       <c r="C73">
-        <v>7.334340415763073</v>
+        <v>0.4485009471160915</v>
       </c>
       <c r="D73">
-        <v>31.00924041576307</v>
+        <v>24.46030094711609</v>
       </c>
       <c r="E73">
-        <v>-0.5801000000000016</v>
+        <v>-0.2432000000000016</v>
       </c>
       <c r="F73">
-        <v>23.9199</v>
+        <v>24.2568</v>
       </c>
       <c r="G73">
         <v>0.245</v>
@@ -7374,45 +7374,45 @@
         <v>2.8425</v>
       </c>
       <c r="M73">
-        <v>3.51144132</v>
+        <v>4.87076544</v>
       </c>
       <c r="N73">
-        <v>-0.6689413200000005</v>
+        <v>-2.02826544</v>
       </c>
       <c r="O73">
-        <v>-0.1939929828000001</v>
+        <v>-0.5881969775999999</v>
       </c>
       <c r="P73">
-        <v>-0.4749483372000004</v>
+        <v>-1.4400684624</v>
       </c>
       <c r="Q73">
-        <v>0.5950516627999994</v>
+        <v>-0.3700684623999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4848588349162123</v>
+        <v>0.5249991396892431</v>
       </c>
       <c r="T73">
-        <v>2.68522917823082</v>
+        <v>2.93072228536802</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.2347540297213339</v>
+        <v>0.1692393136467684</v>
       </c>
       <c r="W73">
-        <v>0.1123381084369082</v>
+        <v>0.1668167458197289</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8094966542114961</v>
+        <v>0.5835838401612705</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7420,22 +7420,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2671078161031929</v>
+        <v>0.2686578161031929</v>
       </c>
       <c r="C74">
-        <v>0.4485009471160915</v>
+        <v>-0.05852306796657558</v>
       </c>
       <c r="D74">
-        <v>24.46030094711609</v>
+        <v>24.29017693203342</v>
       </c>
       <c r="E74">
-        <v>-0.2432000000000016</v>
+        <v>0.09369999999999834</v>
       </c>
       <c r="F74">
-        <v>24.2568</v>
+        <v>24.5937</v>
       </c>
       <c r="G74">
         <v>0.245</v>
@@ -7456,37 +7456,37 @@
         <v>2.8425</v>
       </c>
       <c r="M74">
-        <v>4.87076544</v>
+        <v>4.93841496</v>
       </c>
       <c r="N74">
-        <v>-2.02826544</v>
+        <v>-2.09591496</v>
       </c>
       <c r="O74">
-        <v>-0.5881969775999999</v>
+        <v>-0.6078153384000001</v>
       </c>
       <c r="P74">
-        <v>-1.4400684624</v>
+        <v>-1.4880996216</v>
       </c>
       <c r="Q74">
-        <v>-0.3700684623999999</v>
+        <v>-0.4180996216000006</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5249991396892431</v>
+        <v>0.54274725597403</v>
       </c>
       <c r="T74">
-        <v>2.93072228536802</v>
+        <v>3.039267555196465</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1692393136467684</v>
+        <v>0.1669209668844839</v>
       </c>
       <c r="W74">
-        <v>0.1668167458197289</v>
+        <v>0.1672822698495957</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5835838401612705</v>
+        <v>0.575589540980979</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7502,22 +7502,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2686578161031929</v>
+        <v>0.2702078161031929</v>
       </c>
       <c r="C75">
-        <v>-0.05852306796657558</v>
+        <v>-0.5631969668371006</v>
       </c>
       <c r="D75">
-        <v>24.29017693203342</v>
+        <v>24.1224030331629</v>
       </c>
       <c r="E75">
-        <v>0.09369999999999834</v>
+        <v>0.4305999999999983</v>
       </c>
       <c r="F75">
-        <v>24.5937</v>
+        <v>24.9306</v>
       </c>
       <c r="G75">
         <v>0.245</v>
@@ -7538,37 +7538,37 @@
         <v>2.8425</v>
       </c>
       <c r="M75">
-        <v>4.93841496</v>
+        <v>5.00606448</v>
       </c>
       <c r="N75">
-        <v>-2.09591496</v>
+        <v>-2.16356448</v>
       </c>
       <c r="O75">
-        <v>-0.6078153384000001</v>
+        <v>-0.6274336992</v>
       </c>
       <c r="P75">
-        <v>-1.4880996216</v>
+        <v>-1.5361307808</v>
       </c>
       <c r="Q75">
-        <v>-0.4180996216000006</v>
+        <v>-0.4661307808000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.54274725597403</v>
+        <v>0.5618606119730311</v>
       </c>
       <c r="T75">
-        <v>3.039267555196465</v>
+        <v>3.156162461165561</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1669209668844839</v>
+        <v>0.1646652781428017</v>
       </c>
       <c r="W75">
-        <v>0.1672822698495957</v>
+        <v>0.1677352121489254</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.575589540980979</v>
+        <v>0.5678113039406956</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7584,22 +7584,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2702078161031929</v>
+        <v>0.2717578161031928</v>
       </c>
       <c r="C76">
-        <v>-0.5631969668371006</v>
+        <v>-1.065569112683676</v>
       </c>
       <c r="D76">
-        <v>24.1224030331629</v>
+        <v>23.95693088731632</v>
       </c>
       <c r="E76">
-        <v>0.4305999999999983</v>
+        <v>0.7674999999999983</v>
       </c>
       <c r="F76">
-        <v>24.9306</v>
+        <v>25.2675</v>
       </c>
       <c r="G76">
         <v>0.245</v>
@@ -7620,37 +7620,37 @@
         <v>2.8425</v>
       </c>
       <c r="M76">
-        <v>5.00606448</v>
+        <v>5.073714</v>
       </c>
       <c r="N76">
-        <v>-2.16356448</v>
+        <v>-2.231214</v>
       </c>
       <c r="O76">
-        <v>-0.6274336992</v>
+        <v>-0.6470520599999999</v>
       </c>
       <c r="P76">
-        <v>-1.5361307808</v>
+        <v>-1.58416194</v>
       </c>
       <c r="Q76">
-        <v>-0.4661307808000004</v>
+        <v>-0.5141619400000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5618606119730311</v>
+        <v>0.5825030364519522</v>
       </c>
       <c r="T76">
-        <v>3.156162461165561</v>
+        <v>3.282408959612182</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1646652781428017</v>
+        <v>0.1624697411008977</v>
       </c>
       <c r="W76">
-        <v>0.1677352121489254</v>
+        <v>0.1681760759869397</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5678113039406956</v>
+        <v>0.5602404865548196</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7666,22 +7666,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2717578161031928</v>
+        <v>0.2733078161031929</v>
       </c>
       <c r="C77">
-        <v>-1.065569112683676</v>
+        <v>-1.565686550710058</v>
       </c>
       <c r="D77">
-        <v>23.95693088731632</v>
+        <v>23.79371344928994</v>
       </c>
       <c r="E77">
-        <v>0.7674999999999983</v>
+        <v>1.104399999999998</v>
       </c>
       <c r="F77">
-        <v>25.2675</v>
+        <v>25.6044</v>
       </c>
       <c r="G77">
         <v>0.245</v>
@@ -7702,37 +7702,37 @@
         <v>2.8425</v>
       </c>
       <c r="M77">
-        <v>5.073714</v>
+        <v>5.14136352</v>
       </c>
       <c r="N77">
-        <v>-2.231214</v>
+        <v>-2.29886352</v>
       </c>
       <c r="O77">
-        <v>-0.6470520599999999</v>
+        <v>-0.6666704207999999</v>
       </c>
       <c r="P77">
-        <v>-1.58416194</v>
+        <v>-1.6321930992</v>
       </c>
       <c r="Q77">
-        <v>-0.5141619400000002</v>
+        <v>-0.5621930991999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5825030364519522</v>
+        <v>0.6048656629707837</v>
       </c>
       <c r="T77">
-        <v>3.282408959612182</v>
+        <v>3.419175999596024</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1624697411008977</v>
+        <v>0.1603319813495701</v>
       </c>
       <c r="W77">
-        <v>0.1681760759869397</v>
+        <v>0.1686053381450063</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5602404865548196</v>
+        <v>0.5528689012054141</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7748,22 +7748,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2733078161031929</v>
+        <v>0.2748578161031929</v>
       </c>
       <c r="C78">
-        <v>-1.565686550710058</v>
+        <v>-2.063595052728548</v>
       </c>
       <c r="D78">
-        <v>23.79371344928994</v>
+        <v>23.63270494727145</v>
       </c>
       <c r="E78">
-        <v>1.104399999999998</v>
+        <v>1.441299999999998</v>
       </c>
       <c r="F78">
-        <v>25.6044</v>
+        <v>25.9413</v>
       </c>
       <c r="G78">
         <v>0.245</v>
@@ -7784,37 +7784,37 @@
         <v>2.8425</v>
       </c>
       <c r="M78">
-        <v>5.14136352</v>
+        <v>5.209013039999999</v>
       </c>
       <c r="N78">
-        <v>-2.29886352</v>
+        <v>-2.36651304</v>
       </c>
       <c r="O78">
-        <v>-0.6666704207999999</v>
+        <v>-0.6862887815999998</v>
       </c>
       <c r="P78">
-        <v>-1.6321930992</v>
+        <v>-1.6802242584</v>
       </c>
       <c r="Q78">
-        <v>-0.5621930991999999</v>
+        <v>-0.6102242583999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6048656629707837</v>
+        <v>0.6291728657086438</v>
       </c>
       <c r="T78">
-        <v>3.419175999596024</v>
+        <v>3.567835825665417</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1603319813495701</v>
+        <v>0.1582497478255497</v>
       </c>
       <c r="W78">
-        <v>0.1686053381450063</v>
+        <v>0.1690234506366296</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5528689012054141</v>
+        <v>0.5456887856053438</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7830,22 +7830,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2748578161031929</v>
+        <v>0.2764078161031929</v>
       </c>
       <c r="C79">
-        <v>-2.063595052728548</v>
+        <v>-2.559339159954632</v>
       </c>
       <c r="D79">
-        <v>23.63270494727145</v>
+        <v>23.47386084004536</v>
       </c>
       <c r="E79">
-        <v>1.441299999999998</v>
+        <v>1.778199999999998</v>
       </c>
       <c r="F79">
-        <v>25.9413</v>
+        <v>26.2782</v>
       </c>
       <c r="G79">
         <v>0.245</v>
@@ -7866,37 +7866,37 @@
         <v>2.8425</v>
       </c>
       <c r="M79">
-        <v>5.209013039999999</v>
+        <v>5.27666256</v>
       </c>
       <c r="N79">
-        <v>-2.36651304</v>
+        <v>-2.43416256</v>
       </c>
       <c r="O79">
-        <v>-0.6862887815999998</v>
+        <v>-0.7059071424000001</v>
       </c>
       <c r="P79">
-        <v>-1.6802242584</v>
+        <v>-1.7282554176</v>
       </c>
       <c r="Q79">
-        <v>-0.6102242583999999</v>
+        <v>-0.6582554176000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6291728657086438</v>
+        <v>0.6556898141499459</v>
       </c>
       <c r="T79">
-        <v>3.567835825665417</v>
+        <v>3.730010181377481</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1582497478255497</v>
+        <v>0.1562209049047093</v>
       </c>
       <c r="W79">
-        <v>0.1690234506366296</v>
+        <v>0.1694308422951344</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5456887856053438</v>
+        <v>0.5386927755334803</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7912,22 +7912,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2764078161031929</v>
+        <v>0.2779578161031929</v>
       </c>
       <c r="C80">
-        <v>-2.559339159954632</v>
+        <v>-3.052962224087434</v>
       </c>
       <c r="D80">
-        <v>23.47386084004536</v>
+        <v>23.31713777591256</v>
       </c>
       <c r="E80">
-        <v>1.778199999999998</v>
+        <v>2.115099999999998</v>
       </c>
       <c r="F80">
-        <v>26.2782</v>
+        <v>26.6151</v>
       </c>
       <c r="G80">
         <v>0.245</v>
@@ -7948,37 +7948,37 @@
         <v>2.8425</v>
       </c>
       <c r="M80">
-        <v>5.27666256</v>
+        <v>5.34431208</v>
       </c>
       <c r="N80">
-        <v>-2.43416256</v>
+        <v>-2.50181208</v>
       </c>
       <c r="O80">
-        <v>-0.7059071424000001</v>
+        <v>-0.7255255032</v>
       </c>
       <c r="P80">
-        <v>-1.7282554176</v>
+        <v>-1.7762865768</v>
       </c>
       <c r="Q80">
-        <v>-0.6582554176000004</v>
+        <v>-0.7062865768000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6556898141499459</v>
+        <v>0.6847321862523242</v>
       </c>
       <c r="T80">
-        <v>3.730010181377481</v>
+        <v>3.907629713824027</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1562209049047093</v>
+        <v>0.1542434250957889</v>
       </c>
       <c r="W80">
-        <v>0.1694308422951344</v>
+        <v>0.1698279202407656</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5386927755334803</v>
+        <v>0.5318738796406515</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7994,22 +7994,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2779578161031929</v>
+        <v>0.2795078161031929</v>
       </c>
       <c r="C81">
-        <v>-3.052962224087434</v>
+        <v>-3.544506446755211</v>
       </c>
       <c r="D81">
-        <v>23.31713777591256</v>
+        <v>23.16249355324479</v>
       </c>
       <c r="E81">
-        <v>2.115099999999998</v>
+        <v>2.451999999999998</v>
       </c>
       <c r="F81">
-        <v>26.6151</v>
+        <v>26.952</v>
       </c>
       <c r="G81">
         <v>0.245</v>
@@ -8030,37 +8030,37 @@
         <v>2.8425</v>
       </c>
       <c r="M81">
-        <v>5.34431208</v>
+        <v>5.4119616</v>
       </c>
       <c r="N81">
-        <v>-2.50181208</v>
+        <v>-2.5694616</v>
       </c>
       <c r="O81">
-        <v>-0.7255255032</v>
+        <v>-0.7451438639999999</v>
       </c>
       <c r="P81">
-        <v>-1.7762865768</v>
+        <v>-1.824317736</v>
       </c>
       <c r="Q81">
-        <v>-0.7062865768000002</v>
+        <v>-0.7543177360000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6847321862523242</v>
+        <v>0.7166787955649405</v>
       </c>
       <c r="T81">
-        <v>3.907629713824027</v>
+        <v>4.10301119951523</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1542434250957889</v>
+        <v>0.1523153822820916</v>
       </c>
       <c r="W81">
-        <v>0.1698279202407656</v>
+        <v>0.170215071237756</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5318738796406515</v>
+        <v>0.5252254561451434</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8076,22 +8076,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2795078161031929</v>
+        <v>0.2810578161031929</v>
       </c>
       <c r="C82">
-        <v>-3.544506446755211</v>
+        <v>-4.0340129174018</v>
       </c>
       <c r="D82">
-        <v>23.16249355324479</v>
+        <v>23.0098870825982</v>
       </c>
       <c r="E82">
-        <v>2.451999999999998</v>
+        <v>2.788900000000002</v>
       </c>
       <c r="F82">
-        <v>26.952</v>
+        <v>27.2889</v>
       </c>
       <c r="G82">
         <v>0.245</v>
@@ -8112,37 +8112,37 @@
         <v>2.8425</v>
       </c>
       <c r="M82">
-        <v>5.4119616</v>
+        <v>5.47961112</v>
       </c>
       <c r="N82">
-        <v>-2.5694616</v>
+        <v>-2.637111120000001</v>
       </c>
       <c r="O82">
-        <v>-0.7451438639999999</v>
+        <v>-0.7647622248000001</v>
       </c>
       <c r="P82">
-        <v>-1.824317736</v>
+        <v>-1.8723488952</v>
       </c>
       <c r="Q82">
-        <v>-0.7543177360000002</v>
+        <v>-0.8023488952000006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7166787955649405</v>
+        <v>0.7519882058578322</v>
       </c>
       <c r="T82">
-        <v>4.10301119951523</v>
+        <v>4.318959157384453</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1523153822820916</v>
+        <v>0.1504349454637941</v>
       </c>
       <c r="W82">
-        <v>0.170215071237756</v>
+        <v>0.1705926629508701</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5252254561451434</v>
+        <v>0.5187411912544626</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8158,22 +8158,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2810578161031929</v>
+        <v>0.2826078161031929</v>
       </c>
       <c r="C83">
-        <v>-4.0340129174018</v>
+        <v>-4.521521649684871</v>
       </c>
       <c r="D83">
-        <v>23.0098870825982</v>
+        <v>22.85927835031513</v>
       </c>
       <c r="E83">
-        <v>2.788900000000002</v>
+        <v>3.125800000000002</v>
       </c>
       <c r="F83">
-        <v>27.2889</v>
+        <v>27.6258</v>
       </c>
       <c r="G83">
         <v>0.245</v>
@@ -8194,37 +8194,37 @@
         <v>2.8425</v>
       </c>
       <c r="M83">
-        <v>5.47961112</v>
+        <v>5.54726064</v>
       </c>
       <c r="N83">
-        <v>-2.637111120000001</v>
+        <v>-2.70476064</v>
       </c>
       <c r="O83">
-        <v>-0.7647622248000001</v>
+        <v>-0.7843805856</v>
       </c>
       <c r="P83">
-        <v>-1.8723488952</v>
+        <v>-1.9203800544</v>
       </c>
       <c r="Q83">
-        <v>-0.8023488952000006</v>
+        <v>-0.8503800544000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7519882058578322</v>
+        <v>0.7912208839610452</v>
       </c>
       <c r="T83">
-        <v>4.318959157384453</v>
+        <v>4.5589013327947</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1504349454637941</v>
+        <v>0.1486003729581381</v>
       </c>
       <c r="W83">
-        <v>0.1705926629508701</v>
+        <v>0.1709610451100059</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5187411912544626</v>
+        <v>0.5124150791659935</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8240,22 +8240,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2826078161031929</v>
+        <v>0.2841578161031929</v>
       </c>
       <c r="C84">
-        <v>-4.521521649684871</v>
+        <v>-5.007071616454375</v>
       </c>
       <c r="D84">
-        <v>22.85927835031513</v>
+        <v>22.71062838354563</v>
       </c>
       <c r="E84">
-        <v>3.125800000000002</v>
+        <v>3.462700000000002</v>
       </c>
       <c r="F84">
-        <v>27.6258</v>
+        <v>27.9627</v>
       </c>
       <c r="G84">
         <v>0.245</v>
@@ -8276,37 +8276,37 @@
         <v>2.8425</v>
       </c>
       <c r="M84">
-        <v>5.54726064</v>
+        <v>5.614910160000001</v>
       </c>
       <c r="N84">
-        <v>-2.70476064</v>
+        <v>-2.772410160000001</v>
       </c>
       <c r="O84">
-        <v>-0.7843805856</v>
+        <v>-0.8039989464000002</v>
       </c>
       <c r="P84">
-        <v>-1.9203800544</v>
+        <v>-1.968411213600001</v>
       </c>
       <c r="Q84">
-        <v>-0.8503800544000004</v>
+        <v>-0.8984112136000011</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7912208839610452</v>
+        <v>0.8350691712528715</v>
       </c>
       <c r="T84">
-        <v>4.5589013327947</v>
+        <v>4.827071999429683</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1486003729581381</v>
+        <v>0.1468100070188834</v>
       </c>
       <c r="W84">
-        <v>0.1709610451100059</v>
+        <v>0.1713205505906082</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5124150791659935</v>
+        <v>0.5062414035133911</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8322,22 +8322,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2841578161031929</v>
+        <v>0.285707816103193</v>
       </c>
       <c r="C85">
-        <v>-5.007071616454375</v>
+        <v>-5.490700783374702</v>
       </c>
       <c r="D85">
-        <v>22.71062838354563</v>
+        <v>22.5638992166253</v>
       </c>
       <c r="E85">
-        <v>3.462700000000002</v>
+        <v>3.799600000000002</v>
       </c>
       <c r="F85">
-        <v>27.9627</v>
+        <v>28.2996</v>
       </c>
       <c r="G85">
         <v>0.245</v>
@@ -8358,37 +8358,37 @@
         <v>2.8425</v>
       </c>
       <c r="M85">
-        <v>5.614910160000001</v>
+        <v>5.682559680000001</v>
       </c>
       <c r="N85">
-        <v>-2.772410160000001</v>
+        <v>-2.840059680000001</v>
       </c>
       <c r="O85">
-        <v>-0.8039989464000002</v>
+        <v>-0.8236173072000001</v>
       </c>
       <c r="P85">
-        <v>-1.968411213600001</v>
+        <v>-2.016442372800001</v>
       </c>
       <c r="Q85">
-        <v>-0.8984112136000011</v>
+        <v>-0.9464423728000009</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8350691712528715</v>
+        <v>0.884398494456176</v>
       </c>
       <c r="T85">
-        <v>4.827071999429683</v>
+        <v>5.128763999394039</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1468100070188834</v>
+        <v>0.1450622688400872</v>
       </c>
       <c r="W85">
-        <v>0.1713205505906082</v>
+        <v>0.1716714964169105</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5062414035133911</v>
+        <v>0.5002147201382316</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8404,22 +8404,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2857078161031928</v>
+        <v>0.3197713480606489</v>
       </c>
       <c r="C86">
-        <v>-5.490700783374685</v>
+        <v>-8.633025903523333</v>
       </c>
       <c r="D86">
-        <v>22.56389921662531</v>
+        <v>19.75847409647666</v>
       </c>
       <c r="E86">
-        <v>3.799599999999998</v>
+        <v>4.136499999999998</v>
       </c>
       <c r="F86">
-        <v>28.2996</v>
+        <v>28.6365</v>
       </c>
       <c r="G86">
         <v>0.245</v>
@@ -8440,45 +8440,45 @@
         <v>2.8425</v>
       </c>
       <c r="M86">
-        <v>5.68255968</v>
+        <v>6.7524867</v>
       </c>
       <c r="N86">
-        <v>-2.84005968</v>
+        <v>-3.9099867</v>
       </c>
       <c r="O86">
-        <v>-0.8236173071999999</v>
+        <v>-1.133896143</v>
       </c>
       <c r="P86">
-        <v>-2.0164423728</v>
+        <v>-2.776090557</v>
       </c>
       <c r="Q86">
-        <v>-0.9464423728000004</v>
+        <v>-1.706090557</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8843984944561752</v>
+        <v>0.9587286071362935</v>
       </c>
       <c r="T86">
-        <v>5.128763999394034</v>
+        <v>5.58335771558227</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1450622688400872</v>
+        <v>0.122077248963704</v>
       </c>
       <c r="W86">
-        <v>0.1716714964169105</v>
+        <v>0.2070141846943586</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5002147201382318</v>
+        <v>0.4209560309093241</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8486,22 +8486,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3197713480606489</v>
+        <v>0.3216713480606488</v>
       </c>
       <c r="C87">
-        <v>-8.633025903523333</v>
+        <v>-9.106007816513632</v>
       </c>
       <c r="D87">
-        <v>19.75847409647666</v>
+        <v>19.62239218348637</v>
       </c>
       <c r="E87">
-        <v>4.136499999999998</v>
+        <v>4.473399999999998</v>
       </c>
       <c r="F87">
-        <v>28.6365</v>
+        <v>28.9734</v>
       </c>
       <c r="G87">
         <v>0.245</v>
@@ -8522,37 +8522,37 @@
         <v>2.8425</v>
       </c>
       <c r="M87">
-        <v>6.7524867</v>
+        <v>6.831927719999999</v>
       </c>
       <c r="N87">
-        <v>-3.9099867</v>
+        <v>-3.98942772</v>
       </c>
       <c r="O87">
-        <v>-1.133896143</v>
+        <v>-1.1569340388</v>
       </c>
       <c r="P87">
-        <v>-2.776090557</v>
+        <v>-2.8324936812</v>
       </c>
       <c r="Q87">
-        <v>-1.706090557</v>
+        <v>-1.7624936812</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.9587286071362935</v>
+        <v>1.023937793360314</v>
       </c>
       <c r="T87">
-        <v>5.58335771558227</v>
+        <v>5.982168980981003</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.122077248963704</v>
+        <v>0.1206577460687772</v>
       </c>
       <c r="W87">
-        <v>0.2070141846943586</v>
+        <v>0.2073489034769823</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4209560309093241</v>
+        <v>0.4160611933406111</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8568,22 +8568,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3216713480606488</v>
+        <v>0.3235713480606488</v>
       </c>
       <c r="C88">
-        <v>-9.106007816513632</v>
+        <v>-9.577128085842787</v>
       </c>
       <c r="D88">
-        <v>19.62239218348637</v>
+        <v>19.48817191415721</v>
       </c>
       <c r="E88">
-        <v>4.473399999999998</v>
+        <v>4.810299999999998</v>
       </c>
       <c r="F88">
-        <v>28.9734</v>
+        <v>29.3103</v>
       </c>
       <c r="G88">
         <v>0.245</v>
@@ -8604,37 +8604,37 @@
         <v>2.8425</v>
       </c>
       <c r="M88">
-        <v>6.831927719999999</v>
+        <v>6.911368739999999</v>
       </c>
       <c r="N88">
-        <v>-3.98942772</v>
+        <v>-4.068868739999999</v>
       </c>
       <c r="O88">
-        <v>-1.1569340388</v>
+        <v>-1.1799719346</v>
       </c>
       <c r="P88">
-        <v>-2.8324936812</v>
+        <v>-2.888896805399999</v>
       </c>
       <c r="Q88">
-        <v>-1.7624936812</v>
+        <v>-1.8188968054</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.023937793360314</v>
+        <v>1.099179162080339</v>
       </c>
       <c r="T88">
-        <v>5.982168980981003</v>
+        <v>6.442335825671849</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1206577460687772</v>
+        <v>0.1192708754243085</v>
       </c>
       <c r="W88">
-        <v>0.2073489034769823</v>
+        <v>0.2076759275749481</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4160611933406111</v>
+        <v>0.4112788807734776</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8650,22 +8650,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3235713480606488</v>
+        <v>0.3254713480606488</v>
       </c>
       <c r="C89">
-        <v>-9.577128085842787</v>
+        <v>-10.04642465379178</v>
       </c>
       <c r="D89">
-        <v>19.48817191415721</v>
+        <v>19.35577534620822</v>
       </c>
       <c r="E89">
-        <v>4.810299999999998</v>
+        <v>5.147199999999998</v>
       </c>
       <c r="F89">
-        <v>29.3103</v>
+        <v>29.6472</v>
       </c>
       <c r="G89">
         <v>0.245</v>
@@ -8686,37 +8686,37 @@
         <v>2.8425</v>
       </c>
       <c r="M89">
-        <v>6.911368739999999</v>
+        <v>6.990809759999999</v>
       </c>
       <c r="N89">
-        <v>-4.068868739999999</v>
+        <v>-4.14830976</v>
       </c>
       <c r="O89">
-        <v>-1.1799719346</v>
+        <v>-1.2030098304</v>
       </c>
       <c r="P89">
-        <v>-2.888896805399999</v>
+        <v>-2.9452999296</v>
       </c>
       <c r="Q89">
-        <v>-1.8188968054</v>
+        <v>-1.8752999296</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.099179162080339</v>
+        <v>1.186960758920367</v>
       </c>
       <c r="T89">
-        <v>6.442335825671849</v>
+        <v>6.979197144477838</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1192708754243085</v>
+        <v>0.1179155245672141</v>
       </c>
       <c r="W89">
-        <v>0.2076759275749481</v>
+        <v>0.2079955193070509</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4112788807734776</v>
+        <v>0.4066052571283244</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8732,22 +8732,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3254713480606488</v>
+        <v>0.3273713480606488</v>
       </c>
       <c r="C90">
-        <v>-10.04642465379178</v>
+        <v>-10.51393443852696</v>
       </c>
       <c r="D90">
-        <v>19.35577534620822</v>
+        <v>19.22516556147303</v>
       </c>
       <c r="E90">
-        <v>5.147199999999998</v>
+        <v>5.484099999999998</v>
       </c>
       <c r="F90">
-        <v>29.6472</v>
+        <v>29.9841</v>
       </c>
       <c r="G90">
         <v>0.245</v>
@@ -8768,37 +8768,37 @@
         <v>2.8425</v>
       </c>
       <c r="M90">
-        <v>6.990809759999999</v>
+        <v>7.070250779999999</v>
       </c>
       <c r="N90">
-        <v>-4.14830976</v>
+        <v>-4.227750779999999</v>
       </c>
       <c r="O90">
-        <v>-1.2030098304</v>
+        <v>-1.2260477262</v>
       </c>
       <c r="P90">
-        <v>-2.9452999296</v>
+        <v>-3.0017030538</v>
       </c>
       <c r="Q90">
-        <v>-1.8752999296</v>
+        <v>-1.9317030538</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.186960758920367</v>
+        <v>1.290702646094946</v>
       </c>
       <c r="T90">
-        <v>6.979197144477838</v>
+        <v>7.613669612157642</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1179155245672141</v>
+        <v>0.116590631032751</v>
       </c>
       <c r="W90">
-        <v>0.2079955193070509</v>
+        <v>0.2083079292024773</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4066052571283244</v>
+        <v>0.4020366587336243</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8814,22 +8814,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3273713480606488</v>
+        <v>0.3292713480606488</v>
       </c>
       <c r="C91">
-        <v>-10.51393443852696</v>
+        <v>-10.9796933684213</v>
       </c>
       <c r="D91">
-        <v>19.22516556147303</v>
+        <v>19.0963066315787</v>
       </c>
       <c r="E91">
-        <v>5.484099999999998</v>
+        <v>5.820999999999998</v>
       </c>
       <c r="F91">
-        <v>29.9841</v>
+        <v>30.321</v>
       </c>
       <c r="G91">
         <v>0.245</v>
@@ -8850,37 +8850,37 @@
         <v>2.8425</v>
       </c>
       <c r="M91">
-        <v>7.070250779999999</v>
+        <v>7.149691799999999</v>
       </c>
       <c r="N91">
-        <v>-4.227750779999999</v>
+        <v>-4.3071918</v>
       </c>
       <c r="O91">
-        <v>-1.2260477262</v>
+        <v>-1.249085622</v>
       </c>
       <c r="P91">
-        <v>-3.0017030538</v>
+        <v>-3.058106178</v>
       </c>
       <c r="Q91">
-        <v>-1.9317030538</v>
+        <v>-1.988106178</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.290702646094946</v>
+        <v>1.415192910704441</v>
       </c>
       <c r="T91">
-        <v>7.613669612157642</v>
+        <v>8.375036573373407</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.116590631032751</v>
+        <v>0.1152951795768315</v>
       </c>
       <c r="W91">
-        <v>0.2083079292024773</v>
+        <v>0.2086133966557831</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4020366587336243</v>
+        <v>0.397569584747695</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8896,22 +8896,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3292713480606488</v>
+        <v>0.3311713480606489</v>
       </c>
       <c r="C92">
-        <v>-10.9796933684213</v>
+        <v>-11.44373641500454</v>
       </c>
       <c r="D92">
-        <v>19.0963066315787</v>
+        <v>18.96916358499545</v>
       </c>
       <c r="E92">
-        <v>5.820999999999998</v>
+        <v>6.157899999999998</v>
       </c>
       <c r="F92">
-        <v>30.321</v>
+        <v>30.6579</v>
       </c>
       <c r="G92">
         <v>0.245</v>
@@ -8932,37 +8932,37 @@
         <v>2.8425</v>
       </c>
       <c r="M92">
-        <v>7.149691799999999</v>
+        <v>7.22913282</v>
       </c>
       <c r="N92">
-        <v>-4.3071918</v>
+        <v>-4.386632820000001</v>
       </c>
       <c r="O92">
-        <v>-1.249085622</v>
+        <v>-1.2721235178</v>
       </c>
       <c r="P92">
-        <v>-3.058106178</v>
+        <v>-3.114509302200001</v>
       </c>
       <c r="Q92">
-        <v>-1.988106178</v>
+        <v>-2.044509302200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.415192910704441</v>
+        <v>1.56734767856049</v>
       </c>
       <c r="T92">
-        <v>8.375036573373407</v>
+        <v>9.30559619263712</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1152951795768315</v>
+        <v>0.1140281995814817</v>
       </c>
       <c r="W92">
-        <v>0.2086133966557831</v>
+        <v>0.2089121505386866</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.397569584747695</v>
+        <v>0.3932006882120059</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8978,22 +8978,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3311713480606489</v>
+        <v>0.3330713480606489</v>
       </c>
       <c r="C93">
-        <v>-11.44373641500454</v>
+        <v>-11.90609762460587</v>
       </c>
       <c r="D93">
-        <v>18.96916358499545</v>
+        <v>18.84370237539413</v>
       </c>
       <c r="E93">
-        <v>6.157899999999998</v>
+        <v>6.494799999999998</v>
       </c>
       <c r="F93">
-        <v>30.6579</v>
+        <v>30.9948</v>
       </c>
       <c r="G93">
         <v>0.245</v>
@@ -9014,37 +9014,37 @@
         <v>2.8425</v>
       </c>
       <c r="M93">
-        <v>7.22913282</v>
+        <v>7.30857384</v>
       </c>
       <c r="N93">
-        <v>-4.386632820000001</v>
+        <v>-4.46607384</v>
       </c>
       <c r="O93">
-        <v>-1.2721235178</v>
+        <v>-1.2951614136</v>
       </c>
       <c r="P93">
-        <v>-3.114509302200001</v>
+        <v>-3.1709124264</v>
       </c>
       <c r="Q93">
-        <v>-2.044509302200001</v>
+        <v>-2.1009124264</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.56734767856049</v>
+        <v>1.757541138380551</v>
       </c>
       <c r="T93">
-        <v>9.30559619263712</v>
+        <v>10.46879571671676</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1140281995814817</v>
+        <v>0.1127887626295091</v>
       </c>
       <c r="W93">
-        <v>0.2089121505386866</v>
+        <v>0.2092044097719618</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3932006882120059</v>
+        <v>0.3889267676879625</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9060,22 +9060,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3330713480606489</v>
+        <v>0.3349713480606489</v>
       </c>
       <c r="C94">
-        <v>-11.90609762460587</v>
+        <v>-12.36681014874896</v>
       </c>
       <c r="D94">
-        <v>18.84370237539413</v>
+        <v>18.71988985125104</v>
       </c>
       <c r="E94">
-        <v>6.494799999999998</v>
+        <v>6.831699999999998</v>
       </c>
       <c r="F94">
-        <v>30.9948</v>
+        <v>31.3317</v>
       </c>
       <c r="G94">
         <v>0.245</v>
@@ -9096,37 +9096,37 @@
         <v>2.8425</v>
       </c>
       <c r="M94">
-        <v>7.30857384</v>
+        <v>7.38801486</v>
       </c>
       <c r="N94">
-        <v>-4.46607384</v>
+        <v>-4.545514860000001</v>
       </c>
       <c r="O94">
-        <v>-1.2951614136</v>
+        <v>-1.3181993094</v>
       </c>
       <c r="P94">
-        <v>-3.1709124264</v>
+        <v>-3.227315550600001</v>
       </c>
       <c r="Q94">
-        <v>-2.1009124264</v>
+        <v>-2.157315550600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.757541138380551</v>
+        <v>2.00207558672063</v>
       </c>
       <c r="T94">
-        <v>10.46879571671676</v>
+        <v>11.96433796196202</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1127887626295091</v>
+        <v>0.1115759802356434</v>
       </c>
       <c r="W94">
-        <v>0.2092044097719618</v>
+        <v>0.2094903838604353</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3889267676879625</v>
+        <v>0.3847447594332531</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9142,22 +9142,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3349713480606489</v>
+        <v>0.3368713480606489</v>
       </c>
       <c r="C95">
-        <v>-12.36681014874896</v>
+        <v>-12.82590627335675</v>
       </c>
       <c r="D95">
-        <v>18.71988985125104</v>
+        <v>18.59769372664325</v>
       </c>
       <c r="E95">
-        <v>6.831699999999998</v>
+        <v>7.168600000000001</v>
       </c>
       <c r="F95">
-        <v>31.3317</v>
+        <v>31.6686</v>
       </c>
       <c r="G95">
         <v>0.245</v>
@@ -9178,37 +9178,37 @@
         <v>2.8425</v>
       </c>
       <c r="M95">
-        <v>7.38801486</v>
+        <v>7.467455880000001</v>
       </c>
       <c r="N95">
-        <v>-4.545514860000001</v>
+        <v>-4.624955880000002</v>
       </c>
       <c r="O95">
-        <v>-1.3181993094</v>
+        <v>-1.3412372052</v>
       </c>
       <c r="P95">
-        <v>-3.227315550600001</v>
+        <v>-3.283718674800001</v>
       </c>
       <c r="Q95">
-        <v>-2.157315550600001</v>
+        <v>-2.213718674800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.00207558672063</v>
+        <v>2.328121517840736</v>
       </c>
       <c r="T95">
-        <v>11.96433796196202</v>
+        <v>13.95839428895569</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1115759802356434</v>
+        <v>0.1103890017224983</v>
       </c>
       <c r="W95">
-        <v>0.2094903838604353</v>
+        <v>0.2097702733938349</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3847447594332531</v>
+        <v>0.3806517300775801</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9224,22 +9224,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3368713480606489</v>
+        <v>0.3387713480606488</v>
       </c>
       <c r="C96">
-        <v>-12.82590627335675</v>
+        <v>-13.28341744681972</v>
       </c>
       <c r="D96">
-        <v>18.59769372664325</v>
+        <v>18.47708255318028</v>
       </c>
       <c r="E96">
-        <v>7.168600000000001</v>
+        <v>7.505499999999998</v>
       </c>
       <c r="F96">
-        <v>31.6686</v>
+        <v>32.0055</v>
       </c>
       <c r="G96">
         <v>0.245</v>
@@ -9260,37 +9260,37 @@
         <v>2.8425</v>
       </c>
       <c r="M96">
-        <v>7.467455880000001</v>
+        <v>7.5468969</v>
       </c>
       <c r="N96">
-        <v>-4.624955880000002</v>
+        <v>-4.704396900000001</v>
       </c>
       <c r="O96">
-        <v>-1.3412372052</v>
+        <v>-1.364275101</v>
       </c>
       <c r="P96">
-        <v>-3.283718674800001</v>
+        <v>-3.340121799000001</v>
       </c>
       <c r="Q96">
-        <v>-2.213718674800001</v>
+        <v>-2.270121799000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.328121517840736</v>
+        <v>2.784585821408884</v>
       </c>
       <c r="T96">
-        <v>13.95839428895569</v>
+        <v>16.75007314674683</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1103890017224983</v>
+        <v>0.1092270122306825</v>
       </c>
       <c r="W96">
-        <v>0.2097702733938349</v>
+        <v>0.2100442705160051</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3806517300775801</v>
+        <v>0.3766448697609741</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9306,22 +9306,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3387713480606488</v>
+        <v>0.3406713480606488</v>
       </c>
       <c r="C97">
-        <v>-13.28341744681972</v>
+        <v>-13.73937430697902</v>
       </c>
       <c r="D97">
-        <v>18.47708255318028</v>
+        <v>18.35802569302098</v>
       </c>
       <c r="E97">
-        <v>7.505499999999998</v>
+        <v>7.842399999999998</v>
       </c>
       <c r="F97">
-        <v>32.0055</v>
+        <v>32.3424</v>
       </c>
       <c r="G97">
         <v>0.245</v>
@@ -9342,37 +9342,37 @@
         <v>2.8425</v>
       </c>
       <c r="M97">
-        <v>7.5468969</v>
+        <v>7.62633792</v>
       </c>
       <c r="N97">
-        <v>-4.704396900000001</v>
+        <v>-4.78383792</v>
       </c>
       <c r="O97">
-        <v>-1.364275101</v>
+        <v>-1.3873129968</v>
       </c>
       <c r="P97">
-        <v>-3.340121799000001</v>
+        <v>-3.3965249232</v>
       </c>
       <c r="Q97">
-        <v>-2.270121799000001</v>
+        <v>-2.3265249232</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.784585821408884</v>
+        <v>3.469282276761107</v>
       </c>
       <c r="T97">
-        <v>16.75007314674683</v>
+        <v>20.93759143343355</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1092270122306825</v>
+        <v>0.1080892308532796</v>
       </c>
       <c r="W97">
-        <v>0.2100442705160051</v>
+        <v>0.2103125593647967</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3766448697609741</v>
+        <v>0.3727214857009641</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9388,22 +9388,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3406713480606488</v>
+        <v>0.3425713480606489</v>
       </c>
       <c r="C98">
-        <v>-13.73937430697902</v>
+        <v>-14.19380670707316</v>
       </c>
       <c r="D98">
-        <v>18.35802569302098</v>
+        <v>18.24049329292684</v>
       </c>
       <c r="E98">
-        <v>7.842399999999998</v>
+        <v>8.179299999999998</v>
       </c>
       <c r="F98">
-        <v>32.3424</v>
+        <v>32.6793</v>
       </c>
       <c r="G98">
         <v>0.245</v>
@@ -9424,37 +9424,37 @@
         <v>2.8425</v>
       </c>
       <c r="M98">
-        <v>7.62633792</v>
+        <v>7.70577894</v>
       </c>
       <c r="N98">
-        <v>-4.78383792</v>
+        <v>-4.863278940000001</v>
       </c>
       <c r="O98">
-        <v>-1.3873129968</v>
+        <v>-1.4103508926</v>
       </c>
       <c r="P98">
-        <v>-3.3965249232</v>
+        <v>-3.4529280474</v>
       </c>
       <c r="Q98">
-        <v>-2.3265249232</v>
+        <v>-2.382928047400001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.469282276761097</v>
+        <v>4.610443035681464</v>
       </c>
       <c r="T98">
-        <v>20.93759143343349</v>
+        <v>27.91678857791133</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1080892308532796</v>
+        <v>0.10697490888572</v>
       </c>
       <c r="W98">
-        <v>0.2103125593647967</v>
+        <v>0.2105753164847473</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3727214857009641</v>
+        <v>0.3688789961576551</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9470,22 +9470,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3425713480606489</v>
+        <v>0.3444713480606488</v>
       </c>
       <c r="C99">
-        <v>-14.19380670707316</v>
+        <v>-14.64674374069422</v>
       </c>
       <c r="D99">
-        <v>18.24049329292684</v>
+        <v>18.12445625930578</v>
       </c>
       <c r="E99">
-        <v>8.179299999999998</v>
+        <v>8.516199999999998</v>
       </c>
       <c r="F99">
-        <v>32.6793</v>
+        <v>33.0162</v>
       </c>
       <c r="G99">
         <v>0.245</v>
@@ -9506,37 +9506,37 @@
         <v>2.8425</v>
       </c>
       <c r="M99">
-        <v>7.70577894</v>
+        <v>7.78521996</v>
       </c>
       <c r="N99">
-        <v>-4.863278940000001</v>
+        <v>-4.94271996</v>
       </c>
       <c r="O99">
-        <v>-1.4103508926</v>
+        <v>-1.4333887884</v>
       </c>
       <c r="P99">
-        <v>-3.4529280474</v>
+        <v>-3.5093311716</v>
       </c>
       <c r="Q99">
-        <v>-2.382928047400001</v>
+        <v>-2.4393311716</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.610443035681464</v>
+        <v>6.892764553522196</v>
       </c>
       <c r="T99">
-        <v>27.91678857791133</v>
+        <v>41.87518286686699</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.10697490888572</v>
+        <v>0.1058833281828045</v>
       </c>
       <c r="W99">
-        <v>0.2105753164847473</v>
+        <v>0.2108327112144947</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3688789961576551</v>
+        <v>0.3651149247682913</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3444713480606488</v>
+        <v>0.3463713480606488</v>
       </c>
       <c r="C100">
-        <v>-14.64674374069422</v>
+        <v>-15.09821376579765</v>
       </c>
       <c r="D100">
-        <v>18.12445625930578</v>
+        <v>18.00988623420235</v>
       </c>
       <c r="E100">
-        <v>8.516199999999998</v>
+        <v>8.853099999999998</v>
       </c>
       <c r="F100">
-        <v>33.0162</v>
+        <v>33.3531</v>
       </c>
       <c r="G100">
         <v>0.245</v>
@@ -9588,37 +9588,37 @@
         <v>2.8425</v>
       </c>
       <c r="M100">
-        <v>7.78521996</v>
+        <v>7.86466098</v>
       </c>
       <c r="N100">
-        <v>-4.94271996</v>
+        <v>-5.022160980000001</v>
       </c>
       <c r="O100">
-        <v>-1.4333887884</v>
+        <v>-1.4564266842</v>
       </c>
       <c r="P100">
-        <v>-3.5093311716</v>
+        <v>-3.5657342958</v>
       </c>
       <c r="Q100">
-        <v>-2.4393311716</v>
+        <v>-2.495734295800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.892764553522196</v>
+        <v>13.73972910704439</v>
       </c>
       <c r="T100">
-        <v>41.87518286686699</v>
+        <v>83.75036573373399</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1058833281828045</v>
+        <v>0.1048137996153014</v>
       </c>
       <c r="W100">
-        <v>0.2108327112144947</v>
+        <v>0.211084906050712</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9626,91 +9626,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3651149247682913</v>
+        <v>0.3614268952251772</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3463713480606488</v>
-      </c>
-      <c r="C101">
-        <v>-15.09821376579765</v>
-      </c>
-      <c r="D101">
-        <v>18.00988623420235</v>
-      </c>
-      <c r="E101">
-        <v>8.853099999999998</v>
-      </c>
-      <c r="F101">
-        <v>33.3531</v>
-      </c>
-      <c r="G101">
-        <v>0.245</v>
-      </c>
-      <c r="H101">
-        <v>9.19</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.9125</v>
-      </c>
-      <c r="K101">
-        <v>1.07</v>
-      </c>
-      <c r="L101">
-        <v>2.8425</v>
-      </c>
-      <c r="M101">
-        <v>7.86466098</v>
-      </c>
-      <c r="N101">
-        <v>-5.022160980000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.4564266842</v>
-      </c>
-      <c r="P101">
-        <v>-3.5657342958</v>
-      </c>
-      <c r="Q101">
-        <v>-2.495734295800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>13.73972910704439</v>
-      </c>
-      <c r="T101">
-        <v>83.75036573373399</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1048137996153014</v>
-      </c>
-      <c r="W101">
-        <v>0.211084906050712</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3614268952251772</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
